--- a/data/hrm_sync_leave_1.xlsx
+++ b/data/hrm_sync_leave_1.xlsx
@@ -64,49 +64,223 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>01920862</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Kiên</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>10/09/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>09/09/2026</t>
+  </si>
+  <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t>03/09/2026</t>
+  </si>
+  <si>
+    <t>04/09/2026</t>
+  </si>
+  <si>
+    <t>02223535</t>
+  </si>
+  <si>
+    <t>Nguyễn Quốc</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
+  </si>
+  <si>
+    <t>02224367</t>
+  </si>
+  <si>
+    <t>Ngô Minh Hiếu</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>16/09/2026</t>
+  </si>
+  <si>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>17/09/2026</t>
+  </si>
+  <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
+  </si>
+  <si>
+    <t>02325365</t>
+  </si>
+  <si>
+    <t>Trần Minh Nhật</t>
+  </si>
+  <si>
+    <t>07/09/2026</t>
+  </si>
+  <si>
+    <t>Buổi sáng/半日休暇 - 午前に</t>
+  </si>
+  <si>
+    <t>08/09/2026</t>
+  </si>
+  <si>
+    <t>02021131</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Anh</t>
+  </si>
+  <si>
+    <t>02020965</t>
+  </si>
+  <si>
+    <t>Hà Xuân Tiến</t>
+  </si>
+  <si>
+    <t>11/09/2026</t>
+  </si>
+  <si>
+    <t>21/09/2026</t>
+  </si>
+  <si>
+    <t>02519007</t>
+  </si>
+  <si>
+    <t>Ninh Quang Trường</t>
+  </si>
+  <si>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>22/09/2026</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t>02020497</t>
+  </si>
+  <si>
+    <t>Vũ Nhân Tài</t>
+  </si>
+  <si>
+    <t>02220255</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Sơn</t>
+  </si>
+  <si>
+    <t>02229894</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tài</t>
+  </si>
+  <si>
+    <t>02317843</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>02022149</t>
+  </si>
+  <si>
+    <t>Nguyễn Xuân Mạnh</t>
+  </si>
+  <si>
+    <t>02325310</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Hậu</t>
+  </si>
+  <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
+    <t>02020390</t>
+  </si>
+  <si>
+    <t>Võ Thiên Tuế</t>
+  </si>
+  <si>
+    <t>02021742</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Dũng</t>
+  </si>
+  <si>
+    <t>TV004792</t>
+  </si>
+  <si>
+    <t>Đặng Lê Minh Tài</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欠勤 /  Nghỉ không lương – HĐTV</t>
+  </si>
+  <si>
     <t>02021645</t>
   </si>
   <si>
     <t>Trịnh Xuân Tỉnh</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
     <t>25/09/2026</t>
   </si>
   <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Buổi chiều/半日休暇 - 午後に</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>10/09/2026</t>
-  </si>
-  <si>
-    <t>02223535</t>
-  </si>
-  <si>
-    <t>Nguyễn Quốc</t>
-  </si>
-  <si>
-    <t>03/09/2026</t>
+    <t>đưa con đi khám bệnh</t>
   </si>
   <si>
     <t>02411884</t>
@@ -115,159 +289,6 @@
     <t>Phan Đình Lâm</t>
   </si>
   <si>
-    <t>16/09/2026</t>
-  </si>
-  <si>
-    <t>Buổi sáng/半日休暇 - 午前に</t>
-  </si>
-  <si>
-    <t>TV004792</t>
-  </si>
-  <si>
-    <t>Đặng Lê Minh Tài</t>
-  </si>
-  <si>
-    <t>08/09/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欠勤 /  Nghỉ không lương – HĐTV</t>
-  </si>
-  <si>
-    <t>đưa con đi khám bệnh</t>
-  </si>
-  <si>
-    <t>02325365</t>
-  </si>
-  <si>
-    <t>Trần Minh Nhật</t>
-  </si>
-  <si>
-    <t>07/09/2026</t>
-  </si>
-  <si>
-    <t>02227708</t>
-  </si>
-  <si>
-    <t>Phạm Việt Khải</t>
-  </si>
-  <si>
-    <t>02519007</t>
-  </si>
-  <si>
-    <t>Ninh Quang Trường</t>
-  </si>
-  <si>
-    <t>04/09/2026</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t>02020965</t>
-  </si>
-  <si>
-    <t>Hà Xuân Tiến</t>
-  </si>
-  <si>
-    <t>11/09/2026</t>
-  </si>
-  <si>
-    <t>21/09/2026</t>
-  </si>
-  <si>
-    <t>02021131</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Anh</t>
-  </si>
-  <si>
-    <t>02645241</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Hoàng</t>
-  </si>
-  <si>
-    <t>22/09/2026</t>
-  </si>
-  <si>
-    <t>01920589</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thiện</t>
-  </si>
-  <si>
-    <t>02020497</t>
-  </si>
-  <si>
-    <t>Vũ Nhân Tài</t>
-  </si>
-  <si>
-    <t>02325310</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Hậu</t>
-  </si>
-  <si>
-    <t>01920862</t>
-  </si>
-  <si>
-    <t>Nguyễn Khắc Kiên</t>
-  </si>
-  <si>
-    <t>17/09/2026</t>
-  </si>
-  <si>
-    <t>02317843</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>02022149</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Mạnh</t>
-  </si>
-  <si>
-    <t>02220255</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Sơn</t>
-  </si>
-  <si>
-    <t>02229894</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tài</t>
-  </si>
-  <si>
-    <t>02020390</t>
-  </si>
-  <si>
-    <t>Võ Thiên Tuế</t>
-  </si>
-  <si>
-    <t>18/09/2026</t>
-  </si>
-  <si>
-    <t>09/09/2026</t>
-  </si>
-  <si>
-    <t>02021742</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Dũng</t>
-  </si>
-  <si>
-    <t>02241656</t>
-  </si>
-  <si>
-    <t>Lương Trọng Ân</t>
-  </si>
-  <si>
     <t>02022158</t>
   </si>
   <si>
@@ -316,27 +337,6 @@
     <t>14/09/2026</t>
   </si>
   <si>
-    <t>02221908</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hoàng</t>
-  </si>
-  <si>
-    <t>02224367</t>
-  </si>
-  <si>
-    <t>Ngô Minh Hiếu</t>
-  </si>
-  <si>
-    <t>15/09/2026</t>
-  </si>
-  <si>
-    <t>02325301</t>
-  </si>
-  <si>
-    <t>Cao Thế Mỹ</t>
-  </si>
-  <si>
     <t>01921551</t>
   </si>
   <si>
@@ -364,6 +364,12 @@
     <t>sinh nhat</t>
   </si>
   <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
     <t>02121404</t>
   </si>
   <si>
@@ -374,12 +380,6 @@
   </si>
   <si>
     <t>ốm</t>
-  </si>
-  <si>
-    <t>02223526</t>
-  </si>
-  <si>
-    <t>Nguyễn Thiên Phú</t>
   </si>
   <si>
     <t>02644075</t>
@@ -918,7 +918,7 @@
         <v>19</v>
       </c>
       <c r="G3" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H3" s="7" t="s">
         <v>20</v>
@@ -962,7 +962,7 @@
         <v>26</v>
       </c>
       <c r="G4" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>20</v>
@@ -1003,10 +1003,10 @@
         <v>29</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G5" s="8">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>20</v>
@@ -1032,10 +1032,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -1044,10 +1044,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G6" s="8">
         <v>0.5</v>
@@ -1056,7 +1056,7 @@
         <v>20</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>22</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -1088,22 +1088,22 @@
         <v>18</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G7" s="8">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I7" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>23</v>
@@ -1138,13 +1138,13 @@
         <v>41</v>
       </c>
       <c r="G8" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H8" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J8" s="7" t="s">
         <v>22</v>
@@ -1176,19 +1176,19 @@
         <v>18</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G9" s="8">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>22</v>
@@ -1220,13 +1220,13 @@
         <v>18</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G10" s="8">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>20</v>
@@ -1252,25 +1252,25 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="F11" s="8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G11" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H11" s="7" t="s">
         <v>20</v>
@@ -1296,10 +1296,10 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>17</v>
@@ -1308,10 +1308,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="G12" s="8">
         <v>1</v>
@@ -1320,7 +1320,7 @@
         <v>20</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>22</v>
@@ -1340,22 +1340,22 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="F13" s="8" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="G13" s="8">
         <v>1</v>
@@ -1364,7 +1364,7 @@
         <v>20</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>22</v>
@@ -1384,31 +1384,31 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="F14" s="8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G14" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J14" s="7" t="s">
         <v>22</v>
@@ -1428,10 +1428,10 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>17</v>
@@ -1440,19 +1440,19 @@
         <v>18</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G15" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J15" s="7" t="s">
         <v>22</v>
@@ -1472,25 +1472,25 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>26</v>
-      </c>
       <c r="F16" s="8" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="G16" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>20</v>
@@ -1516,11 +1516,11 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>62</v>
-      </c>
       <c r="C17" s="7" t="s">
         <v>17</v>
       </c>
@@ -1528,10 +1528,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="G17" s="8">
         <v>1</v>
@@ -1540,7 +1540,7 @@
         <v>20</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>22</v>
@@ -1560,11 +1560,11 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="C18" s="7" t="s">
         <v>17</v>
       </c>
@@ -1572,10 +1572,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="G18" s="8">
         <v>1</v>
@@ -1584,7 +1584,7 @@
         <v>20</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>22</v>
@@ -1604,10 +1604,10 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>17</v>
@@ -1616,10 +1616,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="G19" s="8">
         <v>1</v>
@@ -1628,7 +1628,7 @@
         <v>20</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>22</v>
@@ -1657,22 +1657,22 @@
         <v>17</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>46</v>
       </c>
       <c r="G20" s="8">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>22</v>
@@ -1692,10 +1692,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>17</v>
@@ -1704,10 +1704,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="G21" s="8">
         <v>1</v>
@@ -1716,7 +1716,7 @@
         <v>20</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J21" s="7" t="s">
         <v>22</v>
@@ -1736,31 +1736,31 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="G22" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J22" s="7" t="s">
         <v>22</v>
@@ -1780,10 +1780,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>17</v>
@@ -1792,13 +1792,13 @@
         <v>18</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G23" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>20</v>
@@ -1824,10 +1824,10 @@
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>17</v>
@@ -1836,19 +1836,19 @@
         <v>18</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="G24" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J24" s="7" t="s">
         <v>22</v>
@@ -1868,10 +1868,10 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>17</v>
@@ -1880,19 +1880,19 @@
         <v>18</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="G25" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J25" s="7" t="s">
         <v>22</v>
@@ -1912,10 +1912,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>17</v>
@@ -1927,16 +1927,16 @@
         <v>29</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G26" s="8">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J26" s="7" t="s">
         <v>22</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>17</v>
@@ -1968,10 +1968,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="G27" s="8">
         <v>0.5</v>
@@ -1980,7 +1980,7 @@
         <v>20</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="J27" s="7" t="s">
         <v>22</v>
@@ -2000,10 +2000,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>17</v>
@@ -2012,13 +2012,13 @@
         <v>18</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="G28" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>20</v>
@@ -2044,10 +2044,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>17</v>
@@ -2056,19 +2056,19 @@
         <v>18</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>78</v>
+        <v>29</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="G29" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>22</v>
@@ -2088,10 +2088,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>17</v>
@@ -2100,19 +2100,19 @@
         <v>18</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G30" s="4">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>22</v>
@@ -2132,10 +2132,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>81</v>
+        <v>44</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>82</v>
+        <v>45</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>17</v>
@@ -2144,19 +2144,19 @@
         <v>18</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G31" s="4">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>22</v>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>83</v>
+        <v>62</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>17</v>
@@ -2188,13 +2188,13 @@
         <v>18</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="G32" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>20</v>
@@ -2220,10 +2220,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>17</v>
@@ -2232,16 +2232,16 @@
         <v>18</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="G33" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="I33" s="3" t="s">
         <v>47</v>
@@ -2264,10 +2264,10 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>17</v>
@@ -2276,19 +2276,19 @@
         <v>18</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>29</v>
+        <v>86</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>46</v>
+        <v>86</v>
       </c>
       <c r="G34" s="4">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>22</v>
@@ -2308,10 +2308,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>17</v>
@@ -2320,22 +2320,22 @@
         <v>18</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G35" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>23</v>
@@ -2352,10 +2352,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>17</v>
@@ -2364,19 +2364,19 @@
         <v>18</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G36" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>22</v>
@@ -2396,11 +2396,11 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="C37" s="3" t="s">
         <v>17</v>
       </c>
@@ -2408,19 +2408,19 @@
         <v>18</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>77</v>
+        <v>19</v>
       </c>
       <c r="G37" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>22</v>
@@ -2440,10 +2440,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>17</v>
@@ -2452,10 +2452,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G38" s="4">
         <v>0.5</v>
@@ -2464,7 +2464,7 @@
         <v>20</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>22</v>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>17</v>
@@ -2496,10 +2496,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="G39" s="4">
         <v>1</v>
@@ -2508,7 +2508,7 @@
         <v>20</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>22</v>
@@ -2528,10 +2528,10 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>17</v>
@@ -2543,7 +2543,7 @@
         <v>29</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G40" s="4">
         <v>2</v>
@@ -2552,7 +2552,7 @@
         <v>20</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>22</v>
@@ -2572,10 +2572,10 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>92</v>
+        <v>65</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>17</v>
@@ -2584,10 +2584,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="G41" s="4">
         <v>1</v>
@@ -2596,7 +2596,7 @@
         <v>20</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>22</v>
@@ -2616,31 +2616,31 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="G42" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>22</v>
@@ -2660,10 +2660,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>17</v>
@@ -2672,19 +2672,19 @@
         <v>18</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>98</v>
+        <v>33</v>
       </c>
       <c r="G43" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J43" s="3" t="s">
         <v>22</v>
@@ -2704,11 +2704,11 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>64</v>
-      </c>
       <c r="C44" s="3" t="s">
         <v>17</v>
       </c>
@@ -2716,19 +2716,19 @@
         <v>18</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="G44" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>22</v>
@@ -2748,10 +2748,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>43</v>
+        <v>95</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>17</v>
@@ -2760,10 +2760,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="G45" s="4">
         <v>1</v>
@@ -2772,7 +2772,7 @@
         <v>20</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>22</v>
@@ -2792,10 +2792,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>17</v>
@@ -2807,7 +2807,7 @@
         <v>29</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G46" s="4">
         <v>2</v>
@@ -2816,7 +2816,7 @@
         <v>20</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>22</v>
@@ -2836,10 +2836,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>17</v>
@@ -2848,19 +2848,19 @@
         <v>18</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G47" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>22</v>
@@ -2880,25 +2880,25 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>77</v>
+        <v>26</v>
       </c>
       <c r="G48" s="4">
-        <v>0.5</v>
+        <v>3</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>20</v>
@@ -2924,10 +2924,10 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>17</v>
@@ -2936,10 +2936,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="G49" s="4">
         <v>1</v>
@@ -2948,7 +2948,7 @@
         <v>20</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>22</v>
@@ -2968,25 +2968,25 @@
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E50" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C50" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="F50" s="4" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
       <c r="G50" s="4">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>20</v>
@@ -3012,10 +3012,10 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>17</v>
@@ -3024,13 +3024,13 @@
         <v>18</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="G51" s="4">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>20</v>
@@ -3056,10 +3056,10 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>17</v>
@@ -3068,13 +3068,13 @@
         <v>18</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>46</v>
       </c>
       <c r="G52" s="4">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>20</v>
@@ -3100,10 +3100,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>74</v>
+        <v>107</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>17</v>
@@ -3112,19 +3112,19 @@
         <v>18</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>41</v>
+        <v>108</v>
       </c>
       <c r="G53" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>22</v>
@@ -3144,10 +3144,10 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>107</v>
+        <v>63</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>17</v>
@@ -3156,10 +3156,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>108</v>
+        <v>53</v>
       </c>
       <c r="G54" s="4">
         <v>1</v>
@@ -3168,7 +3168,7 @@
         <v>20</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>22</v>
@@ -3188,10 +3188,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>87</v>
+        <v>15</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>88</v>
+        <v>16</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>17</v>
@@ -3200,19 +3200,19 @@
         <v>18</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="G55" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>22</v>
@@ -3232,10 +3232,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>17</v>
@@ -3244,10 +3244,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="G56" s="4">
         <v>1</v>
@@ -3256,7 +3256,7 @@
         <v>20</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>22</v>
@@ -3276,10 +3276,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>17</v>
@@ -3288,10 +3288,10 @@
         <v>18</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>98</v>
+        <v>30</v>
       </c>
       <c r="G57" s="4">
         <v>1</v>
@@ -3300,7 +3300,7 @@
         <v>20</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>22</v>
@@ -3329,13 +3329,13 @@
         <v>17</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="G58" s="4">
         <v>1</v>
@@ -3344,13 +3344,13 @@
         <v>113</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>114</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L58" s="3" t="s">
         <v>23</v>
@@ -3373,28 +3373,28 @@
         <v>17</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>103</v>
+        <v>30</v>
       </c>
       <c r="G59" s="4">
         <v>1</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>117</v>
+        <v>20</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>118</v>
+        <v>22</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L59" s="3" t="s">
         <v>23</v>
@@ -3408,37 +3408,37 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G60" s="4">
         <v>1</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>23</v>
@@ -3461,13 +3461,13 @@
         <v>17</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>77</v>
+        <v>33</v>
       </c>
       <c r="G61" s="4">
         <v>0.5</v>
@@ -3476,13 +3476,13 @@
         <v>20</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>23</v>
@@ -3505,13 +3505,13 @@
         <v>17</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G62" s="4">
         <v>1</v>
@@ -3520,13 +3520,13 @@
         <v>20</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>23</v>
@@ -3549,13 +3549,13 @@
         <v>17</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="G63" s="4">
         <v>2</v>
@@ -3564,13 +3564,13 @@
         <v>20</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>23</v>
@@ -3593,10 +3593,10 @@
         <v>17</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>129</v>
@@ -3608,13 +3608,13 @@
         <v>20</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>23</v>
@@ -3637,13 +3637,13 @@
         <v>17</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="G65" s="4">
         <v>0.5</v>
@@ -3652,13 +3652,13 @@
         <v>20</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>23</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G66" s="4">
         <v>1</v>
@@ -3696,13 +3696,13 @@
         <v>20</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>23</v>
@@ -3725,13 +3725,13 @@
         <v>17</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="G67" s="4">
         <v>0.5</v>
@@ -3740,13 +3740,13 @@
         <v>20</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>23</v>
@@ -3760,16 +3760,16 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>129</v>
@@ -3784,13 +3784,13 @@
         <v>20</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J68" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>23</v>
@@ -3813,13 +3813,13 @@
         <v>17</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G69" s="4">
         <v>1</v>
@@ -3828,13 +3828,13 @@
         <v>113</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>134</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>23</v>
@@ -3857,13 +3857,13 @@
         <v>17</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G70" s="4">
         <v>1</v>
@@ -3872,13 +3872,13 @@
         <v>20</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J70" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>23</v>
@@ -3901,7 +3901,7 @@
         <v>17</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>29</v>
@@ -3916,13 +3916,13 @@
         <v>20</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L71" s="3" t="s">
         <v>23</v>

--- a/data/hrm_sync_leave_1.xlsx
+++ b/data/hrm_sync_leave_1.xlsx
@@ -64,64 +64,292 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>01920507</t>
+  </si>
+  <si>
+    <t>Hồ Thị Mỹ</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>04/09/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
     <t>01920862</t>
   </si>
   <si>
     <t>Nguyễn Khắc Kiên</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
+    <t>17/09/2026</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
+  </si>
+  <si>
+    <t>01921551</t>
+  </si>
+  <si>
+    <t>Trương Quang Nghĩa</t>
+  </si>
+  <si>
+    <t>24/09/2026</t>
+  </si>
+  <si>
+    <t>02020390</t>
+  </si>
+  <si>
+    <t>Võ Thiên Tuế</t>
+  </si>
+  <si>
+    <t>03/09/2026</t>
+  </si>
+  <si>
+    <t>02020497</t>
+  </si>
+  <si>
+    <t>Vũ Nhân Tài</t>
+  </si>
+  <si>
+    <t>11/09/2026</t>
+  </si>
+  <si>
+    <t>02020488</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trúc</t>
+  </si>
+  <si>
+    <t>14/09/2026</t>
+  </si>
+  <si>
+    <t>02229894</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tài</t>
+  </si>
+  <si>
+    <t>07/09/2026</t>
+  </si>
+  <si>
+    <t>Buổi sáng/半日休暇 - 午前に</t>
+  </si>
+  <si>
+    <t>02325365</t>
+  </si>
+  <si>
+    <t>Trần Minh Nhật</t>
+  </si>
+  <si>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>08/09/2026</t>
+  </si>
+  <si>
+    <t>02519007</t>
+  </si>
+  <si>
+    <t>Ninh Quang Trường</t>
+  </si>
+  <si>
+    <t>02020965</t>
+  </si>
+  <si>
+    <t>Hà Xuân Tiến</t>
+  </si>
+  <si>
+    <t>02223535</t>
+  </si>
+  <si>
+    <t>Nguyễn Quốc</t>
+  </si>
+  <si>
+    <t>21/09/2026</t>
+  </si>
+  <si>
+    <t>02021131</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Anh</t>
+  </si>
+  <si>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>22/09/2026</t>
+  </si>
+  <si>
+    <t>02220255</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Sơn</t>
+  </si>
+  <si>
+    <t>02317843</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>02022149</t>
+  </si>
+  <si>
+    <t>Nguyễn Xuân Mạnh</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
   </si>
   <si>
     <t>10/09/2026</t>
   </si>
   <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
+    <t>02325310</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Hậu</t>
+  </si>
+  <si>
+    <t>TV004792</t>
+  </si>
+  <si>
+    <t>Đặng Lê Minh Tài</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欠勤 /  Nghỉ không lương – HĐTV</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
   </si>
   <si>
     <t>09/09/2026</t>
   </si>
   <si>
+    <t>02021742</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Dũng</t>
+  </si>
+  <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
+    <t>02021645</t>
+  </si>
+  <si>
+    <t>Trịnh Xuân Tỉnh</t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
+  </si>
+  <si>
+    <t>đưa con đi khám bệnh</t>
+  </si>
+  <si>
+    <t>02411884</t>
+  </si>
+  <si>
+    <t>Phan Đình Lâm</t>
+  </si>
+  <si>
+    <t>16/09/2026</t>
+  </si>
+  <si>
+    <t>28/09/2026</t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
+  </si>
+  <si>
+    <t>02022158</t>
+  </si>
+  <si>
+    <t>Bùi Lê Đức Minh</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t>02619486</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Huy</t>
+  </si>
+  <si>
+    <t>02645269</t>
+  </si>
+  <si>
+    <t>Lê Thanh Toàn</t>
+  </si>
+  <si>
+    <t>02020752</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gián tiếp</t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
     <t>02221908</t>
   </si>
   <si>
     <t>Nguyễn Minh Hoàng</t>
   </si>
   <si>
-    <t>03/09/2026</t>
-  </si>
-  <si>
-    <t>04/09/2026</t>
-  </si>
-  <si>
-    <t>02223535</t>
-  </si>
-  <si>
-    <t>Nguyễn Quốc</t>
-  </si>
-  <si>
-    <t>18/09/2026</t>
-  </si>
-  <si>
-    <t>Buổi chiều/半日休暇 - 午後に</t>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
   </si>
   <si>
     <t>02224367</t>
@@ -133,225 +361,6 @@
     <t>15/09/2026</t>
   </si>
   <si>
-    <t>16/09/2026</t>
-  </si>
-  <si>
-    <t>02227708</t>
-  </si>
-  <si>
-    <t>Phạm Việt Khải</t>
-  </si>
-  <si>
-    <t>17/09/2026</t>
-  </si>
-  <si>
-    <t>02325301</t>
-  </si>
-  <si>
-    <t>Cao Thế Mỹ</t>
-  </si>
-  <si>
-    <t>02325365</t>
-  </si>
-  <si>
-    <t>Trần Minh Nhật</t>
-  </si>
-  <si>
-    <t>07/09/2026</t>
-  </si>
-  <si>
-    <t>Buổi sáng/半日休暇 - 午前に</t>
-  </si>
-  <si>
-    <t>08/09/2026</t>
-  </si>
-  <si>
-    <t>02021131</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Anh</t>
-  </si>
-  <si>
-    <t>02020965</t>
-  </si>
-  <si>
-    <t>Hà Xuân Tiến</t>
-  </si>
-  <si>
-    <t>11/09/2026</t>
-  </si>
-  <si>
-    <t>21/09/2026</t>
-  </si>
-  <si>
-    <t>02519007</t>
-  </si>
-  <si>
-    <t>Ninh Quang Trường</t>
-  </si>
-  <si>
-    <t>02645241</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Hoàng</t>
-  </si>
-  <si>
-    <t>22/09/2026</t>
-  </si>
-  <si>
-    <t>01920589</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thiện</t>
-  </si>
-  <si>
-    <t>02020497</t>
-  </si>
-  <si>
-    <t>Vũ Nhân Tài</t>
-  </si>
-  <si>
-    <t>02220255</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Sơn</t>
-  </si>
-  <si>
-    <t>02229894</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tài</t>
-  </si>
-  <si>
-    <t>02317843</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>02022149</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Mạnh</t>
-  </si>
-  <si>
-    <t>02325310</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Hậu</t>
-  </si>
-  <si>
-    <t>02241656</t>
-  </si>
-  <si>
-    <t>Lương Trọng Ân</t>
-  </si>
-  <si>
-    <t>02020390</t>
-  </si>
-  <si>
-    <t>Võ Thiên Tuế</t>
-  </si>
-  <si>
-    <t>02021742</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Dũng</t>
-  </si>
-  <si>
-    <t>TV004792</t>
-  </si>
-  <si>
-    <t>Đặng Lê Minh Tài</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欠勤 /  Nghỉ không lương – HĐTV</t>
-  </si>
-  <si>
-    <t>02021645</t>
-  </si>
-  <si>
-    <t>Trịnh Xuân Tỉnh</t>
-  </si>
-  <si>
-    <t>25/09/2026</t>
-  </si>
-  <si>
-    <t>đưa con đi khám bệnh</t>
-  </si>
-  <si>
-    <t>02411884</t>
-  </si>
-  <si>
-    <t>Phan Đình Lâm</t>
-  </si>
-  <si>
-    <t>02022158</t>
-  </si>
-  <si>
-    <t>Bùi Lê Đức Minh</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
-    <t>01920507</t>
-  </si>
-  <si>
-    <t>Hồ Thị Mỹ</t>
-  </si>
-  <si>
-    <t>02619486</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Huy</t>
-  </si>
-  <si>
-    <t>02645269</t>
-  </si>
-  <si>
-    <t>Lê Thanh Toàn</t>
-  </si>
-  <si>
-    <t>02020752</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t>02243991</t>
-  </si>
-  <si>
-    <t>Bùi Quang Chưởng</t>
-  </si>
-  <si>
-    <t>14/09/2026</t>
-  </si>
-  <si>
-    <t>01921551</t>
-  </si>
-  <si>
-    <t>Trương Quang Nghĩa</t>
-  </si>
-  <si>
-    <t>24/09/2026</t>
-  </si>
-  <si>
-    <t>02020488</t>
-  </si>
-  <si>
-    <t>Lê Thanh Trúc</t>
-  </si>
-  <si>
     <t>02644066</t>
   </si>
   <si>
@@ -364,70 +373,70 @@
     <t>sinh nhat</t>
   </si>
   <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>無給休暇 / Nghỉ BHXH</t>
+  </si>
+  <si>
+    <t>ốm</t>
+  </si>
+  <si>
     <t>02223526</t>
   </si>
   <si>
     <t>Nguyễn Thiên Phú</t>
   </si>
   <si>
-    <t>02121404</t>
-  </si>
-  <si>
-    <t>Lê Hoàng Minh Tâm</t>
-  </si>
-  <si>
-    <t>無給休暇 / Nghỉ BHXH</t>
-  </si>
-  <si>
-    <t>ốm</t>
-  </si>
-  <si>
     <t>02644075</t>
   </si>
   <si>
     <t>Huỳnh Đại Nhân</t>
   </si>
   <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
+  </si>
+  <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>23/09/2026</t>
+  </si>
+  <si>
     <t>02223605</t>
   </si>
   <si>
     <t>Võ Minh Bắc</t>
   </si>
   <si>
-    <t>02222350</t>
-  </si>
-  <si>
-    <t>Hoàng Văn Nguyên</t>
-  </si>
-  <si>
     <t>02243654</t>
   </si>
   <si>
     <t>Lưu Văn Giang</t>
   </si>
   <si>
-    <t>23/09/2026</t>
-  </si>
-  <si>
-    <t>02020947</t>
-  </si>
-  <si>
-    <t>Nguyễn Hoàng Duy</t>
-  </si>
-  <si>
     <t>02228947</t>
   </si>
   <si>
     <t>Phạm Lê Minh Tân</t>
   </si>
   <si>
+    <t>02224358</t>
+  </si>
+  <si>
+    <t>Hoàng Trung Hiếu</t>
+  </si>
+  <si>
     <t>nghỉ phép sinh nhật</t>
-  </si>
-  <si>
-    <t>02224358</t>
-  </si>
-  <si>
-    <t>Hoàng Trung Hiếu</t>
   </si>
 </sst>
 </file>
@@ -944,10 +953,10 @@
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>17</v>
@@ -956,19 +965,19 @@
         <v>18</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G4" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H4" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J4" s="7" t="s">
         <v>22</v>
@@ -988,10 +997,10 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>17</v>
@@ -1000,13 +1009,13 @@
         <v>18</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G5" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>20</v>
@@ -1032,10 +1041,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -1044,19 +1053,19 @@
         <v>18</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="G6" s="8">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H6" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J6" s="7" t="s">
         <v>22</v>
@@ -1076,10 +1085,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -1088,13 +1097,13 @@
         <v>18</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>38</v>
       </c>
       <c r="G7" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>20</v>
@@ -1176,19 +1185,19 @@
         <v>18</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G9" s="8">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>22</v>
@@ -1208,22 +1217,22 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="F10" s="8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G10" s="8">
         <v>0.5</v>
@@ -1232,7 +1241,7 @@
         <v>20</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>22</v>
@@ -1252,10 +1261,10 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>17</v>
@@ -1264,10 +1273,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G11" s="8">
         <v>0.5</v>
@@ -1276,7 +1285,7 @@
         <v>20</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J11" s="7" t="s">
         <v>22</v>
@@ -1296,10 +1305,10 @@
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>17</v>
@@ -1308,13 +1317,13 @@
         <v>18</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G12" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>20</v>
@@ -1340,10 +1349,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>17</v>
@@ -1352,10 +1361,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G13" s="8">
         <v>1</v>
@@ -1384,10 +1393,10 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>17</v>
@@ -1396,10 +1405,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G14" s="8">
         <v>1</v>
@@ -1428,10 +1437,10 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>17</v>
@@ -1440,13 +1449,13 @@
         <v>18</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G15" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
         <v>20</v>
@@ -1472,10 +1481,10 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>17</v>
@@ -1484,10 +1493,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G16" s="8">
         <v>0.5</v>
@@ -1496,7 +1505,7 @@
         <v>20</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>22</v>
@@ -1516,10 +1525,10 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>17</v>
@@ -1528,10 +1537,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="G17" s="8">
         <v>1</v>
@@ -1560,10 +1569,10 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>17</v>
@@ -1572,19 +1581,19 @@
         <v>18</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="G18" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>22</v>
@@ -1604,10 +1613,10 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>17</v>
@@ -1616,10 +1625,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="G19" s="8">
         <v>1</v>
@@ -1648,31 +1657,31 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="C20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>18</v>
-      </c>
       <c r="E20" s="8" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="G20" s="8">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>22</v>
@@ -1692,10 +1701,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>17</v>
@@ -1704,10 +1713,10 @@
         <v>18</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="G21" s="8">
         <v>1</v>
@@ -1736,25 +1745,25 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G22" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
         <v>20</v>
@@ -1780,22 +1789,22 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>54</v>
-      </c>
       <c r="F23" s="8" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="G23" s="8">
         <v>1</v>
@@ -1836,10 +1845,10 @@
         <v>18</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="G24" s="8">
         <v>1</v>
@@ -1868,10 +1877,10 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>17</v>
@@ -1880,10 +1889,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G25" s="8">
         <v>1</v>
@@ -1924,19 +1933,19 @@
         <v>18</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G26" s="8">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="J26" s="7" t="s">
         <v>22</v>
@@ -1956,10 +1965,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>17</v>
@@ -1968,10 +1977,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="G27" s="8">
         <v>0.5</v>
@@ -1980,7 +1989,7 @@
         <v>20</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J27" s="7" t="s">
         <v>22</v>
@@ -2000,10 +2009,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>17</v>
@@ -2012,19 +2021,19 @@
         <v>18</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="G28" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="J28" s="7" t="s">
         <v>22</v>
@@ -2044,25 +2053,25 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E29" s="8" t="s">
-        <v>29</v>
-      </c>
       <c r="F29" s="8" t="s">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="G29" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>20</v>
@@ -2088,10 +2097,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>17</v>
@@ -2100,10 +2109,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G30" s="4">
         <v>0.5</v>
@@ -2112,7 +2121,7 @@
         <v>20</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J30" s="3" t="s">
         <v>22</v>
@@ -2132,22 +2141,22 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="F31" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G31" s="4">
         <v>0.5</v>
@@ -2156,7 +2165,7 @@
         <v>20</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>22</v>
@@ -2176,10 +2185,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>17</v>
@@ -2188,19 +2197,19 @@
         <v>18</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G32" s="4">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>22</v>
@@ -2220,10 +2229,10 @@
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>17</v>
@@ -2232,19 +2241,19 @@
         <v>18</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G33" s="4">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>22</v>
@@ -2288,7 +2297,7 @@
         <v>20</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>22</v>
@@ -2308,10 +2317,10 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>17</v>
@@ -2320,19 +2329,19 @@
         <v>18</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G35" s="4">
         <v>0.5</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>87</v>
@@ -2352,10 +2361,10 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>17</v>
@@ -2364,10 +2373,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G36" s="4">
         <v>0.5</v>
@@ -2376,7 +2385,7 @@
         <v>20</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>22</v>
@@ -2408,10 +2417,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>19</v>
+        <v>72</v>
       </c>
       <c r="G37" s="4">
         <v>0.5</v>
@@ -2420,7 +2429,7 @@
         <v>20</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J37" s="3" t="s">
         <v>22</v>
@@ -2452,10 +2461,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="G38" s="4">
         <v>0.5</v>
@@ -2464,7 +2473,7 @@
         <v>20</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>22</v>
@@ -2484,31 +2493,31 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E39" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="C39" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>53</v>
-      </c>
       <c r="F39" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="G39" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>22</v>
@@ -2519,19 +2528,17 @@
       <c r="L39" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M39" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="M39" s="3"/>
       <c r="N39" s="4" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>17</v>
@@ -2540,13 +2547,13 @@
         <v>18</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="G40" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>20</v>
@@ -2572,11 +2579,11 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B41" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="C41" s="3" t="s">
         <v>17</v>
       </c>
@@ -2584,10 +2591,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="G41" s="4">
         <v>1</v>
@@ -2616,10 +2623,10 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>17</v>
@@ -2628,13 +2635,13 @@
         <v>18</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="G42" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>20</v>
@@ -2660,10 +2667,10 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>17</v>
@@ -2672,10 +2679,10 @@
         <v>18</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="G43" s="4">
         <v>1</v>
@@ -2704,10 +2711,10 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>17</v>
@@ -2716,19 +2723,19 @@
         <v>18</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="G44" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J44" s="3" t="s">
         <v>22</v>
@@ -2748,10 +2755,10 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>95</v>
+        <v>16</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>17</v>
@@ -2760,10 +2767,10 @@
         <v>18</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G45" s="4">
         <v>1</v>
@@ -2792,10 +2799,10 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>17</v>
@@ -2804,10 +2811,10 @@
         <v>18</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G46" s="4">
         <v>2</v>
@@ -2836,10 +2843,10 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>17</v>
@@ -2848,10 +2855,10 @@
         <v>18</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G47" s="4">
         <v>1</v>
@@ -2880,22 +2887,22 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="G48" s="4">
         <v>3</v>
@@ -2924,10 +2931,10 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>17</v>
@@ -2936,19 +2943,19 @@
         <v>18</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="G49" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>22</v>
@@ -2963,15 +2970,15 @@
         <v>22</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>17</v>
@@ -2980,10 +2987,10 @@
         <v>18</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>105</v>
+        <v>41</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>105</v>
+        <v>41</v>
       </c>
       <c r="G50" s="4">
         <v>0.5</v>
@@ -2992,7 +2999,7 @@
         <v>20</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>22</v>
@@ -3012,25 +3019,25 @@
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B51" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C51" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="F51" s="4" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="G51" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>20</v>
@@ -3056,10 +3063,10 @@
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>17</v>
@@ -3068,10 +3075,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G52" s="4">
         <v>0.5</v>
@@ -3080,7 +3087,7 @@
         <v>20</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>22</v>
@@ -3100,10 +3107,10 @@
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>106</v>
+        <v>26</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>17</v>
@@ -3112,10 +3119,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>108</v>
+        <v>79</v>
       </c>
       <c r="G53" s="4">
         <v>1</v>
@@ -3144,10 +3151,10 @@
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>17</v>
@@ -3156,10 +3163,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="G54" s="4">
         <v>1</v>
@@ -3188,10 +3195,10 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>15</v>
+        <v>107</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>17</v>
@@ -3200,19 +3207,19 @@
         <v>18</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="G55" s="4">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>22</v>
@@ -3232,10 +3239,10 @@
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>109</v>
+        <v>26</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>110</v>
+        <v>27</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>17</v>
@@ -3244,10 +3251,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="G56" s="4">
         <v>1</v>
@@ -3276,10 +3283,10 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>17</v>
@@ -3288,13 +3295,13 @@
         <v>18</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="G57" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>20</v>
@@ -3320,40 +3327,40 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="G58" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>114</v>
+        <v>22</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M58" s="3" t="s">
         <v>22</v>
@@ -3364,25 +3371,25 @@
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>102</v>
+        <v>18</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>30</v>
+        <v>113</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="G59" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>20</v>
@@ -3394,10 +3401,10 @@
         <v>22</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>101</v>
+        <v>23</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M59" s="3" t="s">
         <v>22</v>
@@ -3408,37 +3415,37 @@
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="G60" s="4">
         <v>1</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L60" s="3" t="s">
         <v>23</v>
@@ -3452,37 +3459,37 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G61" s="4">
+        <v>1</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B61" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D61" s="3" t="s">
+      <c r="K61" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="E61" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="G61" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="L61" s="3" t="s">
         <v>23</v>
@@ -3496,22 +3503,22 @@
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B62" s="3" t="s">
-        <v>124</v>
-      </c>
       <c r="C62" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="G62" s="4">
         <v>1</v>
@@ -3526,7 +3533,7 @@
         <v>22</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L62" s="3" t="s">
         <v>23</v>
@@ -3540,37 +3547,37 @@
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B63" s="3" t="s">
-        <v>126</v>
-      </c>
       <c r="C63" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D63" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G63" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K63" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="E63" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G63" s="4">
-        <v>2</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="L63" s="3" t="s">
         <v>23</v>
@@ -3584,22 +3591,22 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B64" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="C64" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>59</v>
+        <v>90</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="G64" s="4">
         <v>2</v>
@@ -3614,7 +3621,7 @@
         <v>22</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L64" s="3" t="s">
         <v>23</v>
@@ -3628,22 +3635,22 @@
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="G65" s="4">
         <v>0.5</v>
@@ -3652,13 +3659,13 @@
         <v>20</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L65" s="3" t="s">
         <v>23</v>
@@ -3672,37 +3679,37 @@
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D66" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G66" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J66" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K66" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="E66" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G66" s="4">
-        <v>1</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="L66" s="3" t="s">
         <v>23</v>
@@ -3716,37 +3723,37 @@
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D67" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G67" s="4">
+        <v>1</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J67" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K67" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="E67" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G67" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="H67" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="L67" s="3" t="s">
         <v>23</v>
@@ -3760,22 +3767,22 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>108</v>
+        <v>32</v>
       </c>
       <c r="G68" s="4">
         <v>2</v>
@@ -3790,7 +3797,7 @@
         <v>22</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L68" s="3" t="s">
         <v>23</v>
@@ -3804,37 +3811,37 @@
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B69" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="C69" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="G69" s="4">
         <v>1</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="I69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>134</v>
+        <v>22</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="L69" s="3" t="s">
         <v>23</v>
@@ -3848,25 +3855,25 @@
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>70</v>
+        <v>103</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="G70" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>20</v>
@@ -3878,7 +3885,7 @@
         <v>22</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="L70" s="3" t="s">
         <v>23</v>
@@ -3892,22 +3899,22 @@
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G71" s="4">
         <v>0.5</v>
@@ -3916,13 +3923,13 @@
         <v>20</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="L71" s="3" t="s">
         <v>23</v>
@@ -3931,6 +3938,138 @@
         <v>22</v>
       </c>
       <c r="N71" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B72" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="G72" s="4">
+        <v>1</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K72" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L72" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M72" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N72" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="G73" s="4">
+        <v>1</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J73" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L73" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M73" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N73" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G74" s="4">
+        <v>1</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N74" s="4" t="s">
         <v>25</v>
       </c>
     </row>

--- a/data/hrm_sync_leave_1.xlsx
+++ b/data/hrm_sync_leave_1.xlsx
@@ -64,49 +64,292 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02022158</t>
+  </si>
+  <si>
+    <t>Bùi Lê Đức Minh</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>03/09/2026</t>
+  </si>
+  <si>
+    <t>04/09/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>11/09/2026</t>
+  </si>
+  <si>
+    <t>02220255</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Sơn</t>
+  </si>
+  <si>
+    <t>09/09/2026</t>
+  </si>
+  <si>
+    <t>02325365</t>
+  </si>
+  <si>
+    <t>Trần Minh Nhật</t>
+  </si>
+  <si>
+    <t>07/09/2026</t>
+  </si>
+  <si>
+    <t>Buổi sáng/半日休暇 - 午前に</t>
+  </si>
+  <si>
+    <t>02645269</t>
+  </si>
+  <si>
+    <t>Lê Thanh Toàn</t>
+  </si>
+  <si>
+    <t>28/09/2026</t>
+  </si>
+  <si>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>08/09/2026</t>
+  </si>
+  <si>
+    <t>02021742</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Dũng</t>
+  </si>
+  <si>
+    <t>02020965</t>
+  </si>
+  <si>
+    <t>Hà Xuân Tiến</t>
+  </si>
+  <si>
+    <t>02223535</t>
+  </si>
+  <si>
+    <t>Nguyễn Quốc</t>
+  </si>
+  <si>
+    <t>21/09/2026</t>
+  </si>
+  <si>
+    <t>02021131</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Anh</t>
+  </si>
+  <si>
+    <t>02519007</t>
+  </si>
+  <si>
+    <t>Ninh Quang Trường</t>
+  </si>
+  <si>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>22/09/2026</t>
+  </si>
+  <si>
+    <t>02325310</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Hậu</t>
+  </si>
+  <si>
+    <t>10/09/2026</t>
+  </si>
+  <si>
+    <t>01920862</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Kiên</t>
+  </si>
+  <si>
+    <t>17/09/2026</t>
+  </si>
+  <si>
+    <t>02229894</t>
+  </si>
+  <si>
+    <t>Nguyễn Hữu Tài</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
+  </si>
+  <si>
+    <t>02317843</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>02022149</t>
+  </si>
+  <si>
+    <t>Nguyễn Xuân Mạnh</t>
+  </si>
+  <si>
+    <t>29/09/2026</t>
+  </si>
+  <si>
+    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
+  </si>
+  <si>
+    <t>Nghỉ khám sức khoẻ nghĩa vụ quân sự</t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t>02020497</t>
+  </si>
+  <si>
+    <t>Vũ Nhân Tài</t>
+  </si>
+  <si>
+    <t>02020390</t>
+  </si>
+  <si>
+    <t>Võ Thiên Tuế</t>
+  </si>
+  <si>
+    <t>18/09/2026</t>
+  </si>
+  <si>
+    <t>TV004792</t>
+  </si>
+  <si>
+    <t>Đặng Lê Minh Tài</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欠勤 /  Nghỉ không lương – HĐTV</t>
+  </si>
+  <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
+    <t>02021645</t>
+  </si>
+  <si>
+    <t>Trịnh Xuân Tỉnh</t>
+  </si>
+  <si>
+    <t>02411884</t>
+  </si>
+  <si>
+    <t>Phan Đình Lâm</t>
+  </si>
+  <si>
+    <t>16/09/2026</t>
+  </si>
+  <si>
+    <t>25/09/2026</t>
+  </si>
+  <si>
+    <t>đưa con đi khám bệnh</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
     <t>01920507</t>
   </si>
   <si>
     <t>Hồ Thị Mỹ</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
-    <t>04/09/2026</t>
-  </si>
-  <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>01920862</t>
-  </si>
-  <si>
-    <t>Nguyễn Khắc Kiên</t>
-  </si>
-  <si>
-    <t>17/09/2026</t>
-  </si>
-  <si>
-    <t>Buổi chiều/半日休暇 - 午後に</t>
+    <t>02619486</t>
+  </si>
+  <si>
+    <t>Nguyễn Đức Huy</t>
+  </si>
+  <si>
+    <t>02020752</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>14/09/2026</t>
+  </si>
+  <si>
+    <t>02224367</t>
+  </si>
+  <si>
+    <t>Ngô Minh Hiếu</t>
+  </si>
+  <si>
+    <t>15/09/2026</t>
+  </si>
+  <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
+  </si>
+  <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
   </si>
   <si>
     <t>01921551</t>
@@ -118,258 +361,18 @@
     <t>24/09/2026</t>
   </si>
   <si>
-    <t>02020390</t>
-  </si>
-  <si>
-    <t>Võ Thiên Tuế</t>
-  </si>
-  <si>
-    <t>03/09/2026</t>
-  </si>
-  <si>
-    <t>02020497</t>
-  </si>
-  <si>
-    <t>Vũ Nhân Tài</t>
-  </si>
-  <si>
-    <t>11/09/2026</t>
-  </si>
-  <si>
     <t>02020488</t>
   </si>
   <si>
     <t>Lê Thanh Trúc</t>
   </si>
   <si>
-    <t>14/09/2026</t>
-  </si>
-  <si>
-    <t>02229894</t>
-  </si>
-  <si>
-    <t>Nguyễn Hữu Tài</t>
-  </si>
-  <si>
-    <t>07/09/2026</t>
-  </si>
-  <si>
-    <t>Buổi sáng/半日休暇 - 午前に</t>
-  </si>
-  <si>
-    <t>02325365</t>
-  </si>
-  <si>
-    <t>Trần Minh Nhật</t>
-  </si>
-  <si>
-    <t>02227708</t>
-  </si>
-  <si>
-    <t>Phạm Việt Khải</t>
-  </si>
-  <si>
-    <t>08/09/2026</t>
-  </si>
-  <si>
-    <t>02519007</t>
-  </si>
-  <si>
-    <t>Ninh Quang Trường</t>
-  </si>
-  <si>
-    <t>02020965</t>
-  </si>
-  <si>
-    <t>Hà Xuân Tiến</t>
-  </si>
-  <si>
-    <t>02223535</t>
-  </si>
-  <si>
-    <t>Nguyễn Quốc</t>
-  </si>
-  <si>
-    <t>21/09/2026</t>
-  </si>
-  <si>
-    <t>02021131</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Anh</t>
-  </si>
-  <si>
-    <t>02645241</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Hoàng</t>
-  </si>
-  <si>
-    <t>22/09/2026</t>
-  </si>
-  <si>
-    <t>02220255</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Sơn</t>
-  </si>
-  <si>
-    <t>02317843</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>02022149</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Mạnh</t>
-  </si>
-  <si>
-    <t>01920589</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thiện</t>
-  </si>
-  <si>
-    <t>10/09/2026</t>
-  </si>
-  <si>
-    <t>02325310</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Hậu</t>
-  </si>
-  <si>
-    <t>TV004792</t>
-  </si>
-  <si>
-    <t>Đặng Lê Minh Tài</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欠勤 /  Nghỉ không lương – HĐTV</t>
-  </si>
-  <si>
-    <t>18/09/2026</t>
-  </si>
-  <si>
-    <t>09/09/2026</t>
-  </si>
-  <si>
-    <t>02021742</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Dũng</t>
-  </si>
-  <si>
-    <t>02241656</t>
-  </si>
-  <si>
-    <t>Lương Trọng Ân</t>
-  </si>
-  <si>
-    <t>02021645</t>
-  </si>
-  <si>
-    <t>Trịnh Xuân Tỉnh</t>
-  </si>
-  <si>
-    <t>25/09/2026</t>
-  </si>
-  <si>
-    <t>đưa con đi khám bệnh</t>
-  </si>
-  <si>
-    <t>02411884</t>
-  </si>
-  <si>
-    <t>Phan Đình Lâm</t>
-  </si>
-  <si>
-    <t>16/09/2026</t>
-  </si>
-  <si>
-    <t>28/09/2026</t>
-  </si>
-  <si>
-    <t>Chưa duyệt</t>
-  </si>
-  <si>
-    <t>02022158</t>
-  </si>
-  <si>
-    <t>Bùi Lê Đức Minh</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
-    <t>02619486</t>
-  </si>
-  <si>
-    <t>Nguyễn Đức Huy</t>
-  </si>
-  <si>
-    <t>02645269</t>
-  </si>
-  <si>
-    <t>Lê Thanh Toàn</t>
-  </si>
-  <si>
-    <t>02020752</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t>Chờ cấp trên gián tiếp</t>
-  </si>
-  <si>
-    <t>02243991</t>
-  </si>
-  <si>
-    <t>Bùi Quang Chưởng</t>
-  </si>
-  <si>
-    <t>02221908</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hoàng</t>
-  </si>
-  <si>
-    <t>02325301</t>
-  </si>
-  <si>
-    <t>Cao Thế Mỹ</t>
-  </si>
-  <si>
-    <t>02224367</t>
-  </si>
-  <si>
-    <t>Ngô Minh Hiếu</t>
-  </si>
-  <si>
-    <t>15/09/2026</t>
-  </si>
-  <si>
     <t>02644066</t>
   </si>
   <si>
     <t>Nguyễn Hữu Tình</t>
   </si>
   <si>
-    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
-  </si>
-  <si>
     <t>sinh nhat</t>
   </si>
   <si>
@@ -397,43 +400,43 @@
     <t>Huỳnh Đại Nhân</t>
   </si>
   <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
+  </si>
+  <si>
     <t>02222350</t>
   </si>
   <si>
     <t>Hoàng Văn Nguyên</t>
   </si>
   <si>
+    <t>02243654</t>
+  </si>
+  <si>
+    <t>Lưu Văn Giang</t>
+  </si>
+  <si>
+    <t>23/09/2026</t>
+  </si>
+  <si>
     <t>02020947</t>
   </si>
   <si>
     <t>Nguyễn Hoàng Duy</t>
   </si>
   <si>
-    <t>23/09/2026</t>
-  </si>
-  <si>
-    <t>02223605</t>
-  </si>
-  <si>
-    <t>Võ Minh Bắc</t>
-  </si>
-  <si>
-    <t>02243654</t>
-  </si>
-  <si>
-    <t>Lưu Văn Giang</t>
+    <t>02224358</t>
+  </si>
+  <si>
+    <t>Hoàng Trung Hiếu</t>
   </si>
   <si>
     <t>02228947</t>
   </si>
   <si>
     <t>Phạm Lê Minh Tân</t>
-  </si>
-  <si>
-    <t>02224358</t>
-  </si>
-  <si>
-    <t>Hoàng Trung Hiếu</t>
   </si>
   <si>
     <t>nghỉ phép sinh nhật</t>
@@ -924,260 +927,260 @@
         <v>19</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H3" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L3" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N3" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" s="2" customFormat="1">
       <c r="A4" s="7" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="F4" s="8" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G4" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L4" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="F5" s="8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G5" s="8">
         <v>1</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N5" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="F6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G6" s="8">
-        <v>2</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>21</v>
-      </c>
       <c r="J6" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L6" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N6" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="F7" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G7" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H7" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L7" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="F8" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G8" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L8" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N8" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="C9" s="7" t="s">
         <v>17</v>
       </c>
@@ -1185,42 +1188,42 @@
         <v>18</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="G9" s="8">
         <v>0.5</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N9" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>17</v>
@@ -1229,42 +1232,42 @@
         <v>18</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="G10" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L10" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>17</v>
@@ -1273,42 +1276,42 @@
         <v>18</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G11" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L11" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>17</v>
@@ -1317,42 +1320,42 @@
         <v>18</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F12" s="8" t="s">
         <v>19</v>
       </c>
       <c r="G12" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K12" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L12" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N12" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>17</v>
@@ -1361,42 +1364,42 @@
         <v>18</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="G13" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L13" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>17</v>
@@ -1405,42 +1408,42 @@
         <v>18</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="G14" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K14" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L14" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>17</v>
@@ -1449,42 +1452,42 @@
         <v>18</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="G15" s="8">
         <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L15" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>17</v>
@@ -1493,42 +1496,42 @@
         <v>18</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="G16" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L16" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>63</v>
+        <v>28</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>17</v>
@@ -1537,42 +1540,42 @@
         <v>18</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="G17" s="8">
         <v>1</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>17</v>
@@ -1581,42 +1584,42 @@
         <v>18</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="G18" s="8">
         <v>0.5</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>17</v>
@@ -1625,87 +1628,87 @@
         <v>18</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="G19" s="8">
         <v>1</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K19" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L19" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="C20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>67</v>
-      </c>
       <c r="E20" s="8" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G20" s="8">
         <v>2</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K20" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L20" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N20" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>69</v>
-      </c>
       <c r="C21" s="7" t="s">
         <v>17</v>
       </c>
@@ -1713,42 +1716,42 @@
         <v>18</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="G21" s="8">
         <v>1</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>17</v>
@@ -1757,42 +1760,40 @@
         <v>18</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="G22" s="8">
         <v>1</v>
       </c>
       <c r="H22" s="7" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>22</v>
+        <v>71</v>
       </c>
       <c r="K22" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L22" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>22</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M22" s="7"/>
       <c r="N22" s="8" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>36</v>
+        <v>73</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>17</v>
@@ -1801,42 +1802,42 @@
         <v>18</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="G23" s="8">
         <v>1</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K23" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L23" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N23" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>17</v>
@@ -1845,42 +1846,42 @@
         <v>18</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G24" s="8">
         <v>1</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K24" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L24" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N24" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>17</v>
@@ -1889,42 +1890,40 @@
         <v>18</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="G25" s="8">
         <v>1</v>
       </c>
       <c r="H25" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L25" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="M25" s="7" t="s">
-        <v>22</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M25" s="7"/>
       <c r="N25" s="8" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>17</v>
@@ -1933,42 +1932,42 @@
         <v>18</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="G26" s="8">
         <v>0.5</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K26" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L26" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N26" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>17</v>
@@ -1977,42 +1976,42 @@
         <v>18</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="G27" s="8">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K27" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L27" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N27" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>17</v>
@@ -2021,42 +2020,42 @@
         <v>18</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>78</v>
+        <v>30</v>
       </c>
       <c r="G28" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K28" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L28" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N28" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>37</v>
+        <v>76</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>17</v>
@@ -2065,42 +2064,42 @@
         <v>18</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="G29" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L29" s="7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N29" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>17</v>
@@ -2109,42 +2108,42 @@
         <v>18</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G30" s="4">
         <v>0.5</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M30" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>17</v>
@@ -2153,42 +2152,42 @@
         <v>18</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G31" s="4">
         <v>0.5</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M31" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>80</v>
+        <v>31</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>81</v>
+        <v>32</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>17</v>
@@ -2197,42 +2196,42 @@
         <v>18</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="G32" s="4">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M32" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>17</v>
@@ -2241,42 +2240,42 @@
         <v>18</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G33" s="4">
         <v>2</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M33" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>17</v>
@@ -2285,42 +2284,42 @@
         <v>18</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="G34" s="4">
         <v>0.5</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M34" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>17</v>
@@ -2329,42 +2328,42 @@
         <v>18</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="G35" s="4">
         <v>0.5</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>77</v>
+        <v>21</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>87</v>
+        <v>23</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M35" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>17</v>
@@ -2373,42 +2372,42 @@
         <v>18</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G36" s="4">
         <v>0.5</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M36" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>84</v>
+        <v>45</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>85</v>
+        <v>46</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>17</v>
@@ -2417,42 +2416,42 @@
         <v>18</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>72</v>
+        <v>19</v>
       </c>
       <c r="G37" s="4">
         <v>0.5</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M37" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>17</v>
@@ -2470,33 +2469,33 @@
         <v>0.5</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M38" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>17</v>
@@ -2505,40 +2504,42 @@
         <v>18</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>91</v>
+        <v>40</v>
       </c>
       <c r="G39" s="4">
         <v>0.5</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>22</v>
+        <v>91</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M39" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="N39" s="4" t="s">
-        <v>92</v>
+        <v>26</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>94</v>
+        <v>56</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>17</v>
@@ -2547,42 +2548,40 @@
         <v>18</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="G40" s="4">
         <v>1</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>22</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="M40" s="3"/>
       <c r="N40" s="4" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>17</v>
@@ -2591,43 +2590,43 @@
         <v>18</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="G41" s="4">
         <v>1</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M41" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="C42" s="3" t="s">
         <v>17</v>
       </c>
@@ -2635,42 +2634,42 @@
         <v>18</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="G42" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M42" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>17</v>
@@ -2679,42 +2678,42 @@
         <v>18</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G43" s="4">
         <v>1</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M43" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>17</v>
@@ -2723,42 +2722,42 @@
         <v>18</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G44" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M44" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
-        <v>15</v>
+        <v>94</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>16</v>
+        <v>95</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>17</v>
@@ -2767,43 +2766,43 @@
         <v>18</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G45" s="4">
         <v>1</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M45" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B46" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="C46" s="3" t="s">
         <v>17</v>
       </c>
@@ -2811,130 +2810,130 @@
         <v>18</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G46" s="4">
         <v>2</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M46" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="C47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="C47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>18</v>
-      </c>
       <c r="E47" s="4" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G47" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M47" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="G48" s="4">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="J48" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>17</v>
@@ -2943,42 +2942,42 @@
         <v>18</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>86</v>
+        <v>40</v>
       </c>
       <c r="G49" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>17</v>
@@ -2987,42 +2986,42 @@
         <v>18</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="G50" s="4">
         <v>0.5</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>17</v>
@@ -3031,42 +3030,42 @@
         <v>18</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G51" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>17</v>
@@ -3075,42 +3074,42 @@
         <v>18</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G52" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>27</v>
+        <v>105</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>17</v>
@@ -3119,42 +3118,42 @@
         <v>18</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G53" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="s">
-        <v>48</v>
+        <v>107</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>17</v>
@@ -3163,42 +3162,42 @@
         <v>18</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G54" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J54" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K54" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>17</v>
@@ -3207,42 +3206,42 @@
         <v>18</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G55" s="4">
         <v>2</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J55" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K55" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N55" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>17</v>
@@ -3251,42 +3250,42 @@
         <v>18</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G56" s="4">
         <v>1</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J56" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L56" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>109</v>
+        <v>38</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>110</v>
+        <v>39</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>17</v>
@@ -3295,42 +3294,42 @@
         <v>18</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="G57" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>17</v>
@@ -3339,42 +3338,42 @@
         <v>18</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="G58" s="4">
         <v>0.5</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>17</v>
@@ -3383,694 +3382,958 @@
         <v>18</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>113</v>
+        <v>19</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="G59" s="4">
         <v>2</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="s">
-        <v>114</v>
+        <v>61</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>115</v>
+        <v>62</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="G60" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J60" s="3" t="s">
-        <v>117</v>
+        <v>23</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N60" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="G61" s="4">
         <v>1</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>120</v>
+        <v>21</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J61" s="3" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N61" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>123</v>
+        <v>76</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G62" s="4">
         <v>1</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J62" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N62" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>124</v>
+        <v>111</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>103</v>
+        <v>18</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="G63" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="L63" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N63" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D64" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E64" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="E64" s="4" t="s">
-        <v>90</v>
-      </c>
       <c r="F64" s="4" t="s">
-        <v>28</v>
+        <v>103</v>
       </c>
       <c r="G64" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="L64" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N64" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="G65" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>22</v>
+        <v>118</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N65" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>19</v>
+        <v>106</v>
       </c>
       <c r="G66" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>20</v>
+        <v>121</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N66" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G67" s="4">
         <v>1</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N67" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>130</v>
+        <v>79</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="G68" s="4">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N68" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G69" s="4">
         <v>1</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N69" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="G70" s="4">
         <v>2</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N70" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>35</v>
+        <v>133</v>
       </c>
       <c r="G71" s="4">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J71" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N71" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="G72" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="J72" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N72" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="G73" s="4">
         <v>1</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>116</v>
+        <v>21</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J73" s="3" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="K73" s="3" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="N73" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G74" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K74" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L74" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M74" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N74" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G75" s="4">
+        <v>2</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K75" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L75" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N75" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C76" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="G76" s="4">
+        <v>1</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K76" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L76" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M76" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N76" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E74" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G74" s="4">
+      <c r="B77" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G77" s="4">
         <v>1</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K74" s="3" t="s">
+      <c r="H77" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J77" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K77" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L77" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M77" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N77" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="L74" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M74" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N74" s="4" t="s">
-        <v>25</v>
+      <c r="E78" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G78" s="4">
+        <v>1</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K78" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L78" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M78" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N78" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G79" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J79" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K79" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L79" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M79" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N79" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G80" s="4">
+        <v>1</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="N80" s="4" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/data/hrm_sync_leave_1.xlsx
+++ b/data/hrm_sync_leave_1.xlsx
@@ -64,39 +64,84 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>02/10/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>01921551</t>
+  </si>
+  <si>
+    <t>Trương Quang Nghĩa</t>
+  </si>
+  <si>
+    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
+  </si>
+  <si>
+    <t>nghỉ phép sn</t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>01/10/2026</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
+  </si>
+  <si>
+    <t>02325374</t>
+  </si>
+  <si>
+    <t>Trương Văn Tình</t>
+  </si>
+  <si>
+    <t>02020488</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trúc</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gián tiếp</t>
+  </si>
+  <si>
     <t>01920507</t>
   </si>
   <si>
     <t>Hồ Thị Mỹ</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
-    <t>01/10/2026</t>
-  </si>
-  <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
     <t>02645278</t>
   </si>
   <si>
@@ -107,51 +152,6 @@
   </si>
   <si>
     <t>việc gia đình</t>
-  </si>
-  <si>
-    <t>02221908</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hoàng</t>
-  </si>
-  <si>
-    <t>02/10/2026</t>
-  </si>
-  <si>
-    <t>01921551</t>
-  </si>
-  <si>
-    <t>Trương Quang Nghĩa</t>
-  </si>
-  <si>
-    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
-  </si>
-  <si>
-    <t>nghỉ phép sn</t>
-  </si>
-  <si>
-    <t>02243991</t>
-  </si>
-  <si>
-    <t>Bùi Quang Chưởng</t>
-  </si>
-  <si>
-    <t>Buổi chiều/半日休暇 - 午後に</t>
-  </si>
-  <si>
-    <t>02325374</t>
-  </si>
-  <si>
-    <t>Trương Văn Tình</t>
-  </si>
-  <si>
-    <t>02020488</t>
-  </si>
-  <si>
-    <t>Lê Thanh Trúc</t>
-  </si>
-  <si>
-    <t>Chưa duyệt</t>
   </si>
   <si>
     <t>02020752</t>
@@ -751,13 +751,13 @@
         <v>32</v>
       </c>
       <c r="G5" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>22</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -789,22 +789,22 @@
         <v>18</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G6" s="8">
         <v>1</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>23</v>
@@ -821,10 +821,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -839,13 +839,13 @@
         <v>19</v>
       </c>
       <c r="G7" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>22</v>
@@ -860,15 +860,15 @@
         <v>22</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>40</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>41</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>17</v>
@@ -909,10 +909,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>42</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>43</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>17</v>
@@ -930,13 +930,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>23</v>
@@ -944,9 +944,11 @@
       <c r="L9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M9" s="7"/>
+      <c r="M9" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="N9" s="8" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" s="2" customFormat="1">
@@ -963,10 +965,10 @@
         <v>47</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G10" s="8">
         <v>0.5</v>
@@ -975,7 +977,7 @@
         <v>20</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>22</v>
@@ -1007,10 +1009,10 @@
         <v>50</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G11" s="8">
         <v>1</v>

--- a/data/hrm_sync_leave_1.xlsx
+++ b/data/hrm_sync_leave_1.xlsx
@@ -133,9 +133,6 @@
     <t>Lê Thanh Trúc</t>
   </si>
   <si>
-    <t>Chờ cấp trên gián tiếp</t>
-  </si>
-  <si>
     <t>01920507</t>
   </si>
   <si>
@@ -154,6 +151,51 @@
     <t>việc gia đình</t>
   </si>
   <si>
+    <t>02645269</t>
+  </si>
+  <si>
+    <t>Lê Thanh Toàn</t>
+  </si>
+  <si>
+    <t>05/10/2026</t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
+  </si>
+  <si>
+    <t>06/10/2026</t>
+  </si>
+  <si>
+    <t>Sinh nhật của bản thân</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khám nghĩa vụ quân sự </t>
+  </si>
+  <si>
+    <t>02021742</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Dũng</t>
+  </si>
+  <si>
+    <t>Buổi sáng/半日休暇 - 午前に</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t>02516134</t>
+  </si>
+  <si>
+    <t>Ngô Xuân Nghĩa</t>
+  </si>
+  <si>
     <t>02020752</t>
   </si>
   <si>
@@ -173,6 +215,12 @@
   </si>
   <si>
     <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
   </si>
 </sst>
 </file>
@@ -860,15 +908,15 @@
         <v>22</v>
       </c>
       <c r="N7" s="8" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>39</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>40</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>17</v>
@@ -909,10 +957,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>17</v>
@@ -930,13 +978,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>23</v>
@@ -953,31 +1001,31 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>45</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>46</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G10" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>22</v>
@@ -988,168 +1036,352 @@
       <c r="L10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="M10" s="7"/>
       <c r="N10" s="8" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G11" s="8">
         <v>1</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="K11" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M11" s="7"/>
+      <c r="N11" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" s="2" customFormat="1">
+      <c r="A12" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="8">
+        <v>1</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="K12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="M11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" s="8" t="s">
+      <c r="L12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="7"/>
+      <c r="N12" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" s="2" customFormat="1">
+      <c r="A13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="7"/>
+      <c r="N13" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" s="2" customFormat="1">
+      <c r="A14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K14" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" s="7"/>
+      <c r="N14" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" s="2" customFormat="1">
+      <c r="A15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="8">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M15" s="7"/>
+      <c r="N15" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" s="2" customFormat="1">
+      <c r="A16" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M16" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" s="2" customFormat="1">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="8"/>
-    </row>
-    <row r="13" s="2" customFormat="1">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="8"/>
-    </row>
-    <row r="14" s="2" customFormat="1">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="8"/>
-    </row>
-    <row r="15" s="2" customFormat="1">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="8"/>
-    </row>
-    <row r="16" s="2" customFormat="1">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="8"/>
-    </row>
     <row r="17" s="2" customFormat="1">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="8"/>
+      <c r="A17" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G17" s="8">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M17" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N17" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="18" s="2" customFormat="1">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="8"/>
+      <c r="A18" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="8">
+        <v>1</v>
+      </c>
+      <c r="H18" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" s="8" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7"/>

--- a/data/hrm_sync_leave_1.xlsx
+++ b/data/hrm_sync_leave_1.xlsx
@@ -64,39 +64,60 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>01920507</t>
+  </si>
+  <si>
+    <t>Hồ Thị Mỹ</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>01/10/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欠勤 /  Nghỉ không lương -  HĐLĐ</t>
+  </si>
+  <si>
+    <t>việc gia đình</t>
+  </si>
+  <si>
     <t>02221908</t>
   </si>
   <si>
     <t>Nguyễn Minh Hoàng</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
     <t>02/10/2026</t>
   </si>
   <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
     <t>01921551</t>
   </si>
   <si>
@@ -115,9 +136,6 @@
     <t>Bùi Quang Chưởng</t>
   </si>
   <si>
-    <t>01/10/2026</t>
-  </si>
-  <si>
     <t>Buổi chiều/半日休暇 - 午後に</t>
   </si>
   <si>
@@ -133,24 +151,6 @@
     <t>Lê Thanh Trúc</t>
   </si>
   <si>
-    <t>01920507</t>
-  </si>
-  <si>
-    <t>Hồ Thị Mỹ</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欠勤 /  Nghỉ không lương -  HĐLĐ</t>
-  </si>
-  <si>
-    <t>việc gia đình</t>
-  </si>
-  <si>
     <t>02645269</t>
   </si>
   <si>
@@ -160,21 +160,24 @@
     <t>05/10/2026</t>
   </si>
   <si>
+    <t>Chờ cấp trên gián tiếp</t>
+  </si>
+  <si>
+    <t>06/10/2026</t>
+  </si>
+  <si>
+    <t>Sinh nhật của bản thân</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khám nghĩa vụ quân sự </t>
+  </si>
+  <si>
     <t>Chưa duyệt</t>
   </si>
   <si>
-    <t>06/10/2026</t>
-  </si>
-  <si>
-    <t>Sinh nhật của bản thân</t>
-  </si>
-  <si>
-    <t>07/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khám nghĩa vụ quân sự </t>
-  </si>
-  <si>
     <t>02021742</t>
   </si>
   <si>
@@ -184,6 +187,12 @@
     <t>Buổi sáng/半日休暇 - 午前に</t>
   </si>
   <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
+  </si>
+  <si>
     <t>01920589</t>
   </si>
   <si>
@@ -196,6 +205,12 @@
     <t>Ngô Xuân Nghĩa</t>
   </si>
   <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
     <t>02020752</t>
   </si>
   <si>
@@ -205,6 +220,12 @@
     <t>Pulverize</t>
   </si>
   <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
     <t>01920668</t>
   </si>
   <si>
@@ -215,12 +236,6 @@
   </si>
   <si>
     <t>Đinh Hoàng Phúc</t>
-  </si>
-  <si>
-    <t>02121404</t>
-  </si>
-  <si>
-    <t>Lê Hoàng Minh Tâm</t>
   </si>
 </sst>
 </file>
@@ -799,13 +814,13 @@
         <v>32</v>
       </c>
       <c r="G5" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>22</v>
@@ -825,10 +840,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -837,22 +852,22 @@
         <v>18</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G6" s="8">
         <v>1</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>23</v>
@@ -869,10 +884,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -887,13 +902,13 @@
         <v>19</v>
       </c>
       <c r="G7" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>22</v>
@@ -913,10 +928,10 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>17</v>
@@ -957,10 +972,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>17</v>
@@ -978,13 +993,13 @@
         <v>1</v>
       </c>
       <c r="H9" s="7" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I9" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="K9" s="7" t="s">
         <v>23</v>
@@ -1036,7 +1051,9 @@
       <c r="L10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="7"/>
+      <c r="M10" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="N10" s="8" t="s">
         <v>47</v>
       </c>
@@ -1064,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>21</v>
@@ -1078,7 +1095,9 @@
       <c r="L11" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M11" s="7"/>
+      <c r="M11" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="N11" s="8" t="s">
         <v>47</v>
       </c>
@@ -1106,7 +1125,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>21</v>
@@ -1122,15 +1141,15 @@
       </c>
       <c r="M12" s="7"/>
       <c r="N12" s="8" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>17</v>
@@ -1151,7 +1170,7 @@
         <v>20</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>22</v>
@@ -1162,17 +1181,19 @@
       <c r="L13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M13" s="7"/>
+      <c r="M13" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="N13" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>17</v>
@@ -1181,10 +1202,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G14" s="8">
         <v>1</v>
@@ -1204,17 +1225,19 @@
       <c r="L14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M14" s="7"/>
+      <c r="M14" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="N14" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>17</v>
@@ -1223,10 +1246,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G15" s="8">
         <v>1</v>
@@ -1246,38 +1269,40 @@
       <c r="L15" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M15" s="7"/>
+      <c r="M15" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="N15" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>60</v>
-      </c>
       <c r="C16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="G16" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>22</v>
@@ -1292,27 +1317,27 @@
         <v>22</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="G17" s="8">
         <v>1</v>
@@ -1327,36 +1352,36 @@
         <v>22</v>
       </c>
       <c r="K17" s="7" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M17" s="7" t="s">
         <v>22</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G18" s="8">
         <v>1</v>
@@ -1371,10 +1396,10 @@
         <v>22</v>
       </c>
       <c r="K18" s="7" t="s">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="L18" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M18" s="7" t="s">
         <v>22</v>
@@ -1384,68 +1409,180 @@
       </c>
     </row>
     <row r="19" s="2" customFormat="1">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="8"/>
+      <c r="A19" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M19" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N19" s="8" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="20" s="2" customFormat="1">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="8"/>
+      <c r="A20" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M20" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N20" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="21" s="2" customFormat="1">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="8"/>
+      <c r="A21" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="8">
+        <v>1</v>
+      </c>
+      <c r="H21" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N21" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="22" s="2" customFormat="1">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
-      <c r="M22" s="7"/>
-      <c r="N22" s="8"/>
+      <c r="A22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G22" s="8">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7"/>

--- a/data/hrm_sync_leave_1.xlsx
+++ b/data/hrm_sync_leave_1.xlsx
@@ -64,93 +64,114 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>02/10/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>01921551</t>
+  </si>
+  <si>
+    <t>Trương Quang Nghĩa</t>
+  </si>
+  <si>
+    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
+  </si>
+  <si>
+    <t>nghỉ phép sn</t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>01/10/2026</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
+  </si>
+  <si>
+    <t>02325374</t>
+  </si>
+  <si>
+    <t>Trương Văn Tình</t>
+  </si>
+  <si>
+    <t>02020488</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trúc</t>
+  </si>
+  <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
+  </si>
+  <si>
+    <t>06/10/2026</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
     <t>01920507</t>
   </si>
   <si>
     <t>Hồ Thị Mỹ</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
-    <t>01/10/2026</t>
-  </si>
-  <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
     <t xml:space="preserve">欠勤 /  Nghỉ không lương -  HĐLĐ</t>
   </si>
   <si>
     <t>việc gia đình</t>
   </si>
   <si>
-    <t>02221908</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hoàng</t>
-  </si>
-  <si>
-    <t>02/10/2026</t>
-  </si>
-  <si>
-    <t>01921551</t>
-  </si>
-  <si>
-    <t>Trương Quang Nghĩa</t>
-  </si>
-  <si>
-    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
-  </si>
-  <si>
-    <t>nghỉ phép sn</t>
-  </si>
-  <si>
-    <t>02243991</t>
-  </si>
-  <si>
-    <t>Bùi Quang Chưởng</t>
-  </si>
-  <si>
-    <t>Buổi chiều/半日休暇 - 午後に</t>
-  </si>
-  <si>
-    <t>02325374</t>
-  </si>
-  <si>
-    <t>Trương Văn Tình</t>
-  </si>
-  <si>
-    <t>02020488</t>
-  </si>
-  <si>
-    <t>Lê Thanh Trúc</t>
-  </si>
-  <si>
     <t>02645269</t>
   </si>
   <si>
@@ -160,55 +181,55 @@
     <t>05/10/2026</t>
   </si>
   <si>
+    <t>Sinh nhật của bản thân</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khám nghĩa vụ quân sự </t>
+  </si>
+  <si>
+    <t>02021742</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Dũng</t>
+  </si>
+  <si>
+    <t>Buổi sáng/半日休暇 - 午前に</t>
+  </si>
+  <si>
+    <t>02516134</t>
+  </si>
+  <si>
+    <t>Ngô Xuân Nghĩa</t>
+  </si>
+  <si>
+    <t>02021159</t>
+  </si>
+  <si>
+    <t>Trần Vương</t>
+  </si>
+  <si>
     <t>Chờ cấp trên gián tiếp</t>
   </si>
   <si>
-    <t>06/10/2026</t>
-  </si>
-  <si>
-    <t>Sinh nhật của bản thân</t>
-  </si>
-  <si>
-    <t>07/10/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khám nghĩa vụ quân sự </t>
+    <t>02222785</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Duy</t>
+  </si>
+  <si>
+    <t>08/10/2026</t>
+  </si>
+  <si>
+    <t>無給休暇 / Nghỉ BHXH</t>
+  </si>
+  <si>
+    <t>bản thân bệnh</t>
   </si>
   <si>
     <t>Chưa duyệt</t>
-  </si>
-  <si>
-    <t>02021742</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Dũng</t>
-  </si>
-  <si>
-    <t>Buổi sáng/半日休暇 - 午前に</t>
-  </si>
-  <si>
-    <t>02325301</t>
-  </si>
-  <si>
-    <t>Cao Thế Mỹ</t>
-  </si>
-  <si>
-    <t>01920589</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thiện</t>
-  </si>
-  <si>
-    <t>02516134</t>
-  </si>
-  <si>
-    <t>Ngô Xuân Nghĩa</t>
-  </si>
-  <si>
-    <t>02241656</t>
-  </si>
-  <si>
-    <t>Lương Trọng Ân</t>
   </si>
   <si>
     <t>02020752</t>
@@ -814,13 +835,13 @@
         <v>32</v>
       </c>
       <c r="G5" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>22</v>
@@ -840,10 +861,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -852,22 +873,22 @@
         <v>18</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G6" s="8">
         <v>1</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>23</v>
@@ -884,10 +905,10 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>37</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>38</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
@@ -902,13 +923,13 @@
         <v>19</v>
       </c>
       <c r="G7" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>22</v>
@@ -928,22 +949,22 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="F8" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G8" s="8">
         <v>1</v>
@@ -972,11 +993,11 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>43</v>
-      </c>
       <c r="C9" s="7" t="s">
         <v>17</v>
       </c>
@@ -984,10 +1005,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G9" s="8">
         <v>1</v>
@@ -1016,11 +1037,11 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>45</v>
-      </c>
       <c r="C10" s="7" t="s">
         <v>17</v>
       </c>
@@ -1028,10 +1049,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G10" s="8">
         <v>1</v>
@@ -1055,15 +1076,15 @@
         <v>22</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>17</v>
@@ -1072,22 +1093,22 @@
         <v>18</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G11" s="8">
         <v>1</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>23</v>
@@ -1099,15 +1120,15 @@
         <v>22</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>17</v>
@@ -1116,22 +1137,22 @@
         <v>18</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G12" s="8">
         <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>23</v>
@@ -1139,17 +1160,19 @@
       <c r="L12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="7"/>
+      <c r="M12" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="N12" s="8" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>17</v>
@@ -1158,22 +1181,22 @@
         <v>18</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G13" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>23</v>
@@ -1185,15 +1208,15 @@
         <v>22</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>17</v>
@@ -1202,10 +1225,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G14" s="8">
         <v>1</v>
@@ -1229,15 +1252,15 @@
         <v>22</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>17</v>
@@ -1246,22 +1269,22 @@
         <v>18</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G15" s="8">
         <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>23</v>
@@ -1273,15 +1296,15 @@
         <v>22</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>17</v>
@@ -1290,22 +1313,22 @@
         <v>18</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G16" s="8">
         <v>1</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>23</v>
@@ -1317,15 +1340,15 @@
         <v>22</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>17</v>
@@ -1334,19 +1357,19 @@
         <v>18</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G17" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>22</v>
@@ -1361,15 +1384,15 @@
         <v>22</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>17</v>
@@ -1378,10 +1401,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G18" s="8">
         <v>1</v>
@@ -1405,15 +1428,15 @@
         <v>22</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>17</v>
@@ -1422,19 +1445,19 @@
         <v>18</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G19" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>22</v>
@@ -1449,27 +1472,27 @@
         <v>22</v>
       </c>
       <c r="N19" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>65</v>
+        <v>39</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="G20" s="8">
         <v>0.5</v>
@@ -1478,7 +1501,7 @@
         <v>20</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>22</v>
@@ -1498,22 +1521,22 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G21" s="8">
         <v>1</v>
@@ -1528,36 +1551,36 @@
         <v>22</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>22</v>
       </c>
       <c r="N21" s="8" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
       <c r="G22" s="8">
         <v>1</v>
@@ -1572,81 +1595,191 @@
         <v>22</v>
       </c>
       <c r="K22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1">
+      <c r="A23" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G23" s="8">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" s="7"/>
+      <c r="N23" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1">
+      <c r="A24" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="L22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="8"/>
-    </row>
-    <row r="24" s="2" customFormat="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="8"/>
+      <c r="C24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G24" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="25" s="2" customFormat="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="8"/>
+      <c r="A25" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G25" s="8">
+        <v>1</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="26" s="2" customFormat="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="8"/>
+      <c r="A26" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="8">
+        <v>1</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7"/>

--- a/data/hrm_sync_leave_1.xlsx
+++ b/data/hrm_sync_leave_1.xlsx
@@ -64,93 +64,186 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>02/10/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>01921551</t>
+  </si>
+  <si>
+    <t>Trương Quang Nghĩa</t>
+  </si>
+  <si>
+    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
+  </si>
+  <si>
+    <t>nghỉ phép sn</t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>01/10/2026</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
+  </si>
+  <si>
+    <t>02325374</t>
+  </si>
+  <si>
+    <t>Trương Văn Tình</t>
+  </si>
+  <si>
+    <t>02020752</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>02020488</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trúc</t>
+  </si>
+  <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
+  </si>
+  <si>
+    <t>06/10/2026</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t>02021159</t>
+  </si>
+  <si>
+    <t>Trần Vương</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t>02223535</t>
+  </si>
+  <si>
+    <t>Nguyễn Quốc</t>
+  </si>
+  <si>
+    <t>08/10/2026</t>
+  </si>
+  <si>
+    <t>09/10/2026</t>
+  </si>
+  <si>
+    <t>無給休暇 / Nghỉ BHXH</t>
+  </si>
+  <si>
+    <t>bản thân bệnh</t>
+  </si>
+  <si>
+    <t>02020497</t>
+  </si>
+  <si>
+    <t>Vũ Nhân Tài</t>
+  </si>
+  <si>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>Buổi sáng/半日休暇 - 午前に</t>
+  </si>
+  <si>
+    <t>01920862</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Kiên</t>
+  </si>
+  <si>
+    <t>12/10/2026</t>
+  </si>
+  <si>
+    <t>02021645</t>
+  </si>
+  <si>
+    <t>Trịnh Xuân Tỉnh</t>
+  </si>
+  <si>
+    <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
+  </si>
+  <si>
     <t>01920507</t>
   </si>
   <si>
     <t>Hồ Thị Mỹ</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
-    <t>01/10/2026</t>
-  </si>
-  <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
     <t xml:space="preserve">欠勤 /  Nghỉ không lương -  HĐLĐ</t>
   </si>
   <si>
     <t>việc gia đình</t>
   </si>
   <si>
-    <t>02221908</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hoàng</t>
-  </si>
-  <si>
-    <t>02/10/2026</t>
-  </si>
-  <si>
-    <t>01921551</t>
-  </si>
-  <si>
-    <t>Trương Quang Nghĩa</t>
-  </si>
-  <si>
-    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
-  </si>
-  <si>
-    <t>nghỉ phép sn</t>
-  </si>
-  <si>
-    <t>02243991</t>
-  </si>
-  <si>
-    <t>Bùi Quang Chưởng</t>
-  </si>
-  <si>
-    <t>Buổi chiều/半日休暇 - 午後に</t>
-  </si>
-  <si>
-    <t>02325374</t>
-  </si>
-  <si>
-    <t>Trương Văn Tình</t>
-  </si>
-  <si>
-    <t>02020488</t>
-  </si>
-  <si>
-    <t>Lê Thanh Trúc</t>
-  </si>
-  <si>
     <t>02645269</t>
   </si>
   <si>
@@ -160,82 +253,88 @@
     <t>05/10/2026</t>
   </si>
   <si>
-    <t>Chờ cấp trên gián tiếp</t>
-  </si>
-  <si>
-    <t>06/10/2026</t>
-  </si>
-  <si>
     <t>Sinh nhật của bản thân</t>
   </si>
   <si>
-    <t>07/10/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Khám nghĩa vụ quân sự </t>
   </si>
   <si>
-    <t>Chưa duyệt</t>
-  </si>
-  <si>
     <t>02021742</t>
   </si>
   <si>
     <t>Nguyễn Ngọc Dũng</t>
   </si>
   <si>
-    <t>Buổi sáng/半日休暇 - 午前に</t>
-  </si>
-  <si>
-    <t>02325301</t>
-  </si>
-  <si>
-    <t>Cao Thế Mỹ</t>
-  </si>
-  <si>
-    <t>01920589</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thiện</t>
-  </si>
-  <si>
     <t>02516134</t>
   </si>
   <si>
     <t>Ngô Xuân Nghĩa</t>
   </si>
   <si>
-    <t>02241656</t>
-  </si>
-  <si>
-    <t>Lương Trọng Ân</t>
-  </si>
-  <si>
-    <t>02020752</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
+    <t>02222785</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Duy</t>
+  </si>
+  <si>
+    <t>02021131</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Anh</t>
+  </si>
+  <si>
+    <t>02022149</t>
+  </si>
+  <si>
+    <t>Nguyễn Xuân Mạnh</t>
+  </si>
+  <si>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>02224358</t>
+  </si>
+  <si>
+    <t>Hoàng Trung Hiếu</t>
+  </si>
+  <si>
+    <t>T Extrusion</t>
+  </si>
+  <si>
+    <t>Đinh Hoàng Phúc</t>
+  </si>
+  <si>
+    <t>02020947</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoàng Duy</t>
+  </si>
+  <si>
+    <t>02228947</t>
+  </si>
+  <si>
+    <t>Phạm Lê Minh Tân</t>
+  </si>
+  <si>
+    <t>02644057</t>
+  </si>
+  <si>
+    <t>Phạm Văn Công</t>
+  </si>
+  <si>
+    <t>01920668</t>
+  </si>
+  <si>
+    <t>Hà Viết Thế Thiện</t>
   </si>
   <si>
     <t>02121404</t>
   </si>
   <si>
     <t>Lê Hoàng Minh Tâm</t>
-  </si>
-  <si>
-    <t>01920668</t>
-  </si>
-  <si>
-    <t>Hà Viết Thế Thiện</t>
-  </si>
-  <si>
-    <t>T Extrusion</t>
-  </si>
-  <si>
-    <t>Đinh Hoàng Phúc</t>
   </si>
 </sst>
 </file>
@@ -814,13 +913,13 @@
         <v>32</v>
       </c>
       <c r="G5" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>22</v>
@@ -840,10 +939,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -852,22 +951,22 @@
         <v>18</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G6" s="8">
         <v>1</v>
       </c>
       <c r="H6" s="7" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>23</v>
@@ -884,16 +983,16 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>18</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>19</v>
@@ -908,7 +1007,7 @@
         <v>20</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>22</v>
@@ -928,11 +1027,11 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>41</v>
-      </c>
       <c r="C8" s="7" t="s">
         <v>17</v>
       </c>
@@ -940,10 +1039,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G8" s="8">
         <v>1</v>
@@ -972,22 +1071,22 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="C9" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="F9" s="8" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G9" s="8">
         <v>1</v>
@@ -1028,10 +1127,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G10" s="8">
         <v>1</v>
@@ -1055,15 +1154,15 @@
         <v>22</v>
       </c>
       <c r="N10" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>17</v>
@@ -1072,22 +1171,22 @@
         <v>18</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G11" s="8">
         <v>1</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I11" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="K11" s="7" t="s">
         <v>23</v>
@@ -1099,15 +1198,15 @@
         <v>22</v>
       </c>
       <c r="N11" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" s="2" customFormat="1">
       <c r="A12" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>17</v>
@@ -1116,22 +1215,22 @@
         <v>18</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G12" s="8">
         <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I12" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="K12" s="7" t="s">
         <v>23</v>
@@ -1139,17 +1238,19 @@
       <c r="L12" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M12" s="7"/>
+      <c r="M12" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="N12" s="8" t="s">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>17</v>
@@ -1158,19 +1259,19 @@
         <v>18</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G13" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="J13" s="7" t="s">
         <v>22</v>
@@ -1185,30 +1286,30 @@
         <v>22</v>
       </c>
       <c r="N13" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>48</v>
-      </c>
       <c r="G14" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" s="7" t="s">
         <v>20</v>
@@ -1229,40 +1330,40 @@
         <v>22</v>
       </c>
       <c r="N14" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="8">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="G15" s="8">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>22</v>
-      </c>
       <c r="K15" s="7" t="s">
         <v>23</v>
       </c>
@@ -1273,15 +1374,15 @@
         <v>22</v>
       </c>
       <c r="N15" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>17</v>
@@ -1290,19 +1391,19 @@
         <v>18</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="G16" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H16" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J16" s="7" t="s">
         <v>22</v>
@@ -1317,15 +1418,15 @@
         <v>22</v>
       </c>
       <c r="N16" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>17</v>
@@ -1334,19 +1435,19 @@
         <v>18</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="G17" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="J17" s="7" t="s">
         <v>22</v>
@@ -1361,15 +1462,15 @@
         <v>22</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>17</v>
@@ -1378,10 +1479,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="G18" s="8">
         <v>1</v>
@@ -1405,15 +1506,15 @@
         <v>22</v>
       </c>
       <c r="N18" s="8" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>17</v>
@@ -1422,10 +1523,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="G19" s="8">
         <v>0.5</v>
@@ -1434,7 +1535,7 @@
         <v>20</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>22</v>
@@ -1445,25 +1546,23 @@
       <c r="L19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M19" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="M19" s="7"/>
       <c r="N19" s="8" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E20" s="8" t="s">
         <v>32</v>
@@ -1472,13 +1571,13 @@
         <v>32</v>
       </c>
       <c r="G20" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="J20" s="7" t="s">
         <v>22</v>
@@ -1498,40 +1597,40 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>66</v>
+        <v>18</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G21" s="8">
         <v>1</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="L21" s="7" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M21" s="7" t="s">
         <v>22</v>
@@ -1542,159 +1641,971 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="8">
+        <v>1</v>
+      </c>
+      <c r="H22" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M22" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N22" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" s="2" customFormat="1">
+      <c r="A23" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" s="8">
+        <v>1</v>
+      </c>
+      <c r="H23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M23" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N23" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" s="2" customFormat="1">
+      <c r="A24" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G24" s="8">
+        <v>1</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" s="2" customFormat="1">
+      <c r="A25" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H25" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M25" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N25" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" s="2" customFormat="1">
+      <c r="A26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="8">
+        <v>1</v>
+      </c>
+      <c r="H26" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K26" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M26" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" s="2" customFormat="1">
+      <c r="A27" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="8">
+        <v>1</v>
+      </c>
+      <c r="H27" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I27" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K27" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M27" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N27" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" s="2" customFormat="1">
+      <c r="A28" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H28" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K28" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M28" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N28" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" s="2" customFormat="1">
+      <c r="A29" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G29" s="8">
+        <v>1</v>
+      </c>
+      <c r="H29" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I29" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="M29" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="N29" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G30" s="4">
+        <v>1</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="4">
+        <v>1</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G32" s="4">
+        <v>1</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F22" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="G22" s="8">
-        <v>1</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="M22" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="N22" s="8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
-      <c r="M23" s="7"/>
-      <c r="N23" s="8"/>
-    </row>
-    <row r="24" s="2" customFormat="1">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="8"/>
-    </row>
-    <row r="25" s="2" customFormat="1">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
-      <c r="M25" s="7"/>
-      <c r="N25" s="8"/>
-    </row>
-    <row r="26" s="2" customFormat="1">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
-      <c r="M26" s="7"/>
-      <c r="N26" s="8"/>
-    </row>
-    <row r="27" s="2" customFormat="1">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
-      <c r="M27" s="7"/>
-      <c r="N27" s="8"/>
-    </row>
-    <row r="28" s="2" customFormat="1">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
-      <c r="M28" s="7"/>
-      <c r="N28" s="8"/>
-    </row>
-    <row r="29" s="2" customFormat="1">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
-      <c r="M29" s="7"/>
-      <c r="N29" s="8"/>
+      <c r="G33" s="4">
+        <v>2</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G34" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G35" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G36" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G37" s="4">
+        <v>1</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G38" s="4">
+        <v>1</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G39" s="4">
+        <v>1</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G40" s="4">
+        <v>1</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G41" s="4">
+        <v>1</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G42" s="4">
+        <v>1</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G43" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>25</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/data/hrm_sync_leave_1.xlsx
+++ b/data/hrm_sync_leave_1.xlsx
@@ -64,63 +64,228 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02325301</t>
+  </si>
+  <si>
+    <t>Cao Thế Mỹ</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>06/10/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>01920589</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Thiện</t>
+  </si>
+  <si>
+    <t>02241656</t>
+  </si>
+  <si>
+    <t>Lương Trọng Ân</t>
+  </si>
+  <si>
+    <t>02645278</t>
+  </si>
+  <si>
+    <t>Moha Mad Nazid</t>
+  </si>
+  <si>
+    <t>02021159</t>
+  </si>
+  <si>
+    <t>Trần Vương</t>
+  </si>
+  <si>
+    <t>07/10/2026</t>
+  </si>
+  <si>
+    <t>08/10/2026</t>
+  </si>
+  <si>
+    <t>無給休暇 / Nghỉ BHXH</t>
+  </si>
+  <si>
+    <t>bản thân bệnh</t>
+  </si>
+  <si>
+    <t>02020497</t>
+  </si>
+  <si>
+    <t>Vũ Nhân Tài</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
+  </si>
+  <si>
+    <t>02227708</t>
+  </si>
+  <si>
+    <t>Phạm Việt Khải</t>
+  </si>
+  <si>
+    <t>09/10/2026</t>
+  </si>
+  <si>
+    <t>Buổi sáng/半日休暇 - 午前に</t>
+  </si>
+  <si>
+    <t>01920862</t>
+  </si>
+  <si>
+    <t>Nguyễn Khắc Kiên</t>
+  </si>
+  <si>
+    <t>12/10/2026</t>
+  </si>
+  <si>
+    <t>02021645</t>
+  </si>
+  <si>
+    <t>Trịnh Xuân Tỉnh</t>
+  </si>
+  <si>
+    <t>13/10/2026</t>
+  </si>
+  <si>
+    <t>01920507</t>
+  </si>
+  <si>
+    <t>Hồ Thị Mỹ</t>
+  </si>
+  <si>
+    <t>01/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欠勤 /  Nghỉ không lương -  HĐLĐ</t>
+  </si>
+  <si>
+    <t>việc gia đình</t>
+  </si>
+  <si>
+    <t>02645269</t>
+  </si>
+  <si>
+    <t>Lê Thanh Toàn</t>
+  </si>
+  <si>
+    <t>05/10/2026</t>
+  </si>
+  <si>
+    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
+  </si>
+  <si>
+    <t>Sinh nhật của bản thân</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khám nghĩa vụ quân sự </t>
+  </si>
+  <si>
+    <t>02021742</t>
+  </si>
+  <si>
+    <t>Nguyễn Ngọc Dũng</t>
+  </si>
+  <si>
+    <t>02516134</t>
+  </si>
+  <si>
+    <t>Ngô Xuân Nghĩa</t>
+  </si>
+  <si>
+    <t>02222785</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Duy</t>
+  </si>
+  <si>
+    <t>02223535</t>
+  </si>
+  <si>
+    <t>Nguyễn Quốc</t>
+  </si>
+  <si>
+    <t>02021131</t>
+  </si>
+  <si>
+    <t>Nguyễn Công Anh</t>
+  </si>
+  <si>
+    <t>02022149</t>
+  </si>
+  <si>
+    <t>Nguyễn Xuân Mạnh</t>
+  </si>
+  <si>
+    <t>02645241</t>
+  </si>
+  <si>
+    <t>Nguyễn Đình Hoàng</t>
+  </si>
+  <si>
+    <t>14/10/2026</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gián tiếp</t>
+  </si>
+  <si>
+    <t>02020390</t>
+  </si>
+  <si>
+    <t>Võ Thiên Tuế</t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>Chưa duyệt</t>
+  </si>
+  <si>
     <t>02221908</t>
   </si>
   <si>
     <t>Nguyễn Minh Hoàng</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
     <t>02/10/2026</t>
   </si>
   <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
     <t>01921551</t>
   </si>
   <si>
     <t>Trương Quang Nghĩa</t>
   </si>
   <si>
-    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
-  </si>
-  <si>
     <t>nghỉ phép sn</t>
   </si>
   <si>
-    <t>02243991</t>
-  </si>
-  <si>
-    <t>Bùi Quang Chưởng</t>
-  </si>
-  <si>
-    <t>01/10/2026</t>
-  </si>
-  <si>
-    <t>Buổi chiều/半日休暇 - 午後に</t>
-  </si>
-  <si>
     <t>02325374</t>
   </si>
   <si>
@@ -142,159 +307,6 @@
     <t>Lê Thanh Trúc</t>
   </si>
   <si>
-    <t>02325301</t>
-  </si>
-  <si>
-    <t>Cao Thế Mỹ</t>
-  </si>
-  <si>
-    <t>06/10/2026</t>
-  </si>
-  <si>
-    <t>01920589</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Thiện</t>
-  </si>
-  <si>
-    <t>02241656</t>
-  </si>
-  <si>
-    <t>Lương Trọng Ân</t>
-  </si>
-  <si>
-    <t>02645278</t>
-  </si>
-  <si>
-    <t>Moha Mad Nazid</t>
-  </si>
-  <si>
-    <t>02021159</t>
-  </si>
-  <si>
-    <t>Trần Vương</t>
-  </si>
-  <si>
-    <t>07/10/2026</t>
-  </si>
-  <si>
-    <t>02223535</t>
-  </si>
-  <si>
-    <t>Nguyễn Quốc</t>
-  </si>
-  <si>
-    <t>08/10/2026</t>
-  </si>
-  <si>
-    <t>09/10/2026</t>
-  </si>
-  <si>
-    <t>無給休暇 / Nghỉ BHXH</t>
-  </si>
-  <si>
-    <t>bản thân bệnh</t>
-  </si>
-  <si>
-    <t>02020497</t>
-  </si>
-  <si>
-    <t>Vũ Nhân Tài</t>
-  </si>
-  <si>
-    <t>02227708</t>
-  </si>
-  <si>
-    <t>Phạm Việt Khải</t>
-  </si>
-  <si>
-    <t>Buổi sáng/半日休暇 - 午前に</t>
-  </si>
-  <si>
-    <t>01920862</t>
-  </si>
-  <si>
-    <t>Nguyễn Khắc Kiên</t>
-  </si>
-  <si>
-    <t>12/10/2026</t>
-  </si>
-  <si>
-    <t>02021645</t>
-  </si>
-  <si>
-    <t>Trịnh Xuân Tỉnh</t>
-  </si>
-  <si>
-    <t>13/10/2026</t>
-  </si>
-  <si>
-    <t>Chưa duyệt</t>
-  </si>
-  <si>
-    <t>01920507</t>
-  </si>
-  <si>
-    <t>Hồ Thị Mỹ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">欠勤 /  Nghỉ không lương -  HĐLĐ</t>
-  </si>
-  <si>
-    <t>việc gia đình</t>
-  </si>
-  <si>
-    <t>02645269</t>
-  </si>
-  <si>
-    <t>Lê Thanh Toàn</t>
-  </si>
-  <si>
-    <t>05/10/2026</t>
-  </si>
-  <si>
-    <t>Sinh nhật của bản thân</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khám nghĩa vụ quân sự </t>
-  </si>
-  <si>
-    <t>02021742</t>
-  </si>
-  <si>
-    <t>Nguyễn Ngọc Dũng</t>
-  </si>
-  <si>
-    <t>02516134</t>
-  </si>
-  <si>
-    <t>Ngô Xuân Nghĩa</t>
-  </si>
-  <si>
-    <t>02222785</t>
-  </si>
-  <si>
-    <t>Nguyễn Anh Duy</t>
-  </si>
-  <si>
-    <t>02021131</t>
-  </si>
-  <si>
-    <t>Nguyễn Công Anh</t>
-  </si>
-  <si>
-    <t>02022149</t>
-  </si>
-  <si>
-    <t>Nguyễn Xuân Mạnh</t>
-  </si>
-  <si>
-    <t>02645241</t>
-  </si>
-  <si>
-    <t>Nguyễn Đình Hoàng</t>
-  </si>
-  <si>
     <t>02224358</t>
   </si>
   <si>
@@ -335,6 +347,18 @@
   </si>
   <si>
     <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>02226596</t>
+  </si>
+  <si>
+    <t>Đoàn Văn Dương</t>
+  </si>
+  <si>
+    <t>02223605</t>
+  </si>
+  <si>
+    <t>Võ Minh Bắc</t>
   </si>
 </sst>
 </file>
@@ -872,13 +896,13 @@
         <v>1</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>23</v>
@@ -895,10 +919,10 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>17</v>
@@ -907,19 +931,19 @@
         <v>18</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="G5" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>22</v>
@@ -939,10 +963,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -983,31 +1007,31 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>17</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G7" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>22</v>
@@ -1027,10 +1051,10 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>17</v>
@@ -1039,22 +1063,22 @@
         <v>18</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="G8" s="8">
         <v>1</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>23</v>
@@ -1071,10 +1095,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>17</v>
@@ -1083,19 +1107,19 @@
         <v>18</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G9" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>22</v>
@@ -1115,10 +1139,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>17</v>
@@ -1133,13 +1157,13 @@
         <v>43</v>
       </c>
       <c r="G10" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>22</v>
@@ -1159,22 +1183,22 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="C11" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>43</v>
-      </c>
       <c r="F11" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G11" s="8">
         <v>1</v>
@@ -1215,19 +1239,19 @@
         <v>18</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G12" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>22</v>
@@ -1247,10 +1271,10 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>17</v>
@@ -1259,10 +1283,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G13" s="8">
         <v>1</v>
@@ -1291,34 +1315,34 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="F14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1</v>
+      </c>
+      <c r="H14" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="8" t="s">
+      <c r="I14" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G14" s="8">
-        <v>2</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>23</v>
@@ -1335,10 +1359,10 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>17</v>
@@ -1347,22 +1371,22 @@
         <v>18</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G15" s="8">
         <v>1</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>23</v>
@@ -1379,34 +1403,34 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="8">
+        <v>1</v>
+      </c>
+      <c r="H16" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="I16" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>23</v>
@@ -1423,34 +1447,34 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="8">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="7" t="s">
         <v>61</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="G17" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>23</v>
@@ -1467,10 +1491,10 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>17</v>
@@ -1479,19 +1503,19 @@
         <v>18</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="G18" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>22</v>
@@ -1511,10 +1535,10 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>67</v>
+        <v>26</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>68</v>
+        <v>27</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>17</v>
@@ -1523,19 +1547,19 @@
         <v>18</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="G19" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>22</v>
@@ -1546,17 +1570,19 @@
       <c r="L19" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="M19" s="7"/>
+      <c r="M19" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="N19" s="8" t="s">
-        <v>70</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>17</v>
@@ -1565,10 +1591,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G20" s="8">
         <v>1</v>
@@ -1597,10 +1623,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>17</v>
@@ -1609,22 +1635,22 @@
         <v>18</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="G21" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>23</v>
@@ -1641,10 +1667,10 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>17</v>
@@ -1653,10 +1679,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="G22" s="8">
         <v>1</v>
@@ -1685,10 +1711,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>17</v>
@@ -1697,22 +1723,22 @@
         <v>18</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G23" s="8">
         <v>1</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>23</v>
@@ -1729,10 +1755,10 @@
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>17</v>
@@ -1741,22 +1767,22 @@
         <v>18</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="G24" s="8">
         <v>1</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="K24" s="7" t="s">
         <v>23</v>
@@ -1773,10 +1799,10 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>17</v>
@@ -1785,19 +1811,19 @@
         <v>18</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="G25" s="8">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="J25" s="7" t="s">
         <v>22</v>
@@ -1817,10 +1843,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>17</v>
@@ -1829,22 +1855,22 @@
         <v>18</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="G26" s="8">
         <v>1</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="K26" s="7" t="s">
         <v>23</v>
@@ -1861,10 +1887,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>17</v>
@@ -1873,13 +1899,13 @@
         <v>18</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="G27" s="8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>20</v>
@@ -1905,10 +1931,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>17</v>
@@ -1917,10 +1943,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="G28" s="8">
         <v>0.5</v>
@@ -1929,7 +1955,7 @@
         <v>20</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J28" s="7" t="s">
         <v>22</v>
@@ -1949,10 +1975,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>17</v>
@@ -1961,19 +1987,19 @@
         <v>18</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G29" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>22</v>
@@ -1993,10 +2019,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>17</v>
@@ -2005,22 +2031,22 @@
         <v>18</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G30" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>23</v>
@@ -2037,10 +2063,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>17</v>
@@ -2049,10 +2075,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G31" s="4">
         <v>1</v>
@@ -2081,10 +2107,10 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>48</v>
+        <v>70</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>17</v>
@@ -2093,22 +2119,22 @@
         <v>18</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="G32" s="4">
         <v>1</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="K32" s="3" t="s">
         <v>23</v>
@@ -2120,15 +2146,15 @@
         <v>22</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>17</v>
@@ -2137,19 +2163,19 @@
         <v>18</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G33" s="4">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>22</v>
@@ -2164,15 +2190,15 @@
         <v>22</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>46</v>
+        <v>80</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>17</v>
@@ -2181,19 +2207,19 @@
         <v>18</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G34" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>22</v>
@@ -2208,15 +2234,15 @@
         <v>22</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>25</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>17</v>
@@ -2225,10 +2251,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="G35" s="4">
         <v>0.5</v>
@@ -2237,7 +2263,7 @@
         <v>20</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J35" s="3" t="s">
         <v>22</v>
@@ -2248,19 +2274,17 @@
       <c r="L35" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>22</v>
-      </c>
+      <c r="M35" s="3"/>
       <c r="N35" s="4" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>17</v>
@@ -2269,19 +2293,19 @@
         <v>18</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="G36" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>63</v>
+        <v>21</v>
       </c>
       <c r="J36" s="3" t="s">
         <v>22</v>
@@ -2301,40 +2325,40 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="G37" s="4">
         <v>1</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M37" s="3" t="s">
         <v>22</v>
@@ -2345,40 +2369,40 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G38" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M38" s="3" t="s">
         <v>22</v>
@@ -2389,22 +2413,22 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="G39" s="4">
         <v>1</v>
@@ -2419,10 +2443,10 @@
         <v>22</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M39" s="3" t="s">
         <v>22</v>
@@ -2433,40 +2457,40 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="G40" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M40" s="3" t="s">
         <v>22</v>
@@ -2477,22 +2501,22 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>94</v>
+        <v>18</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="G41" s="4">
         <v>1</v>
@@ -2507,10 +2531,10 @@
         <v>22</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>95</v>
+        <v>23</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>22</v>
@@ -2521,22 +2545,22 @@
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="G42" s="4">
         <v>1</v>
@@ -2551,7 +2575,7 @@
         <v>22</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>37</v>
+        <v>99</v>
       </c>
       <c r="L42" s="3" t="s">
         <v>23</v>
@@ -2565,46 +2589,398 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G43" s="4">
+        <v>1</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G44" s="4">
+        <v>1</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B45" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="G43" s="4">
+      <c r="C45" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G45" s="4">
+        <v>1</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G46" s="4">
+        <v>1</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G47" s="4">
+        <v>1</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M47" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G48" s="4">
         <v>0.5</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N43" s="4" t="s">
-        <v>25</v>
+      <c r="H48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G49" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G50" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G51" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/data/hrm_sync_leave_1.xlsx
+++ b/data/hrm_sync_leave_1.xlsx
@@ -64,39 +64,93 @@
     <t>Trạng thái duyệt</t>
   </si>
   <si>
+    <t>02221908</t>
+  </si>
+  <si>
+    <t>Nguyễn Minh Hoàng</t>
+  </si>
+  <si>
+    <t>Plastic Extrusion</t>
+  </si>
+  <si>
+    <t>TU Extrusion</t>
+  </si>
+  <si>
+    <t>02/10/2026</t>
+  </si>
+  <si>
+    <t>有給休暇 / Nghỉ phép năm</t>
+  </si>
+  <si>
+    <t>Cả ngày/終日休暇</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Thân Trọng Tuấn</t>
+  </si>
+  <si>
+    <t>Nguyễn Thành Thân</t>
+  </si>
+  <si>
+    <t>Đã duyệt</t>
+  </si>
+  <si>
+    <t>01921551</t>
+  </si>
+  <si>
+    <t>Trương Quang Nghĩa</t>
+  </si>
+  <si>
+    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
+  </si>
+  <si>
+    <t>nghỉ phép sn</t>
+  </si>
+  <si>
+    <t>02243991</t>
+  </si>
+  <si>
+    <t>Bùi Quang Chưởng</t>
+  </si>
+  <si>
+    <t>01/10/2026</t>
+  </si>
+  <si>
+    <t>Buổi chiều/半日休暇 - 午後に</t>
+  </si>
+  <si>
+    <t>02325374</t>
+  </si>
+  <si>
+    <t>Trương Văn Tình</t>
+  </si>
+  <si>
+    <t>02020752</t>
+  </si>
+  <si>
+    <t>Nguyễn Chí Cường</t>
+  </si>
+  <si>
+    <t>Pulverize</t>
+  </si>
+  <si>
+    <t>02020488</t>
+  </si>
+  <si>
+    <t>Lê Thanh Trúc</t>
+  </si>
+  <si>
     <t>02325301</t>
   </si>
   <si>
     <t>Cao Thế Mỹ</t>
   </si>
   <si>
-    <t>Plastic Extrusion</t>
-  </si>
-  <si>
-    <t>TU Extrusion</t>
-  </si>
-  <si>
     <t>06/10/2026</t>
   </si>
   <si>
-    <t>有給休暇 / Nghỉ phép năm</t>
-  </si>
-  <si>
-    <t>Cả ngày/終日休暇</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Thân Trọng Tuấn</t>
-  </si>
-  <si>
-    <t>Nguyễn Thành Thân</t>
-  </si>
-  <si>
-    <t>Đã duyệt</t>
-  </si>
-  <si>
     <t>01920589</t>
   </si>
   <si>
@@ -124,6 +178,12 @@
     <t>07/10/2026</t>
   </si>
   <si>
+    <t>02222785</t>
+  </si>
+  <si>
+    <t>Nguyễn Anh Duy</t>
+  </si>
+  <si>
     <t>08/10/2026</t>
   </si>
   <si>
@@ -139,9 +199,6 @@
     <t>Vũ Nhân Tài</t>
   </si>
   <si>
-    <t>Buổi chiều/半日休暇 - 午後に</t>
-  </si>
-  <si>
     <t>02227708</t>
   </si>
   <si>
@@ -178,9 +235,6 @@
     <t>Hồ Thị Mỹ</t>
   </si>
   <si>
-    <t>01/10/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">欠勤 /  Nghỉ không lương -  HĐLĐ</t>
   </si>
   <si>
@@ -196,9 +250,6 @@
     <t>05/10/2026</t>
   </si>
   <si>
-    <t>特別有給休暇 / Nghỉ có lương CĐ đặc biệt</t>
-  </si>
-  <si>
     <t>Sinh nhật của bản thân</t>
   </si>
   <si>
@@ -211,16 +262,19 @@
     <t>Nguyễn Ngọc Dũng</t>
   </si>
   <si>
+    <t>15/10/2026</t>
+  </si>
+  <si>
     <t>02516134</t>
   </si>
   <si>
     <t>Ngô Xuân Nghĩa</t>
   </si>
   <si>
-    <t>02222785</t>
-  </si>
-  <si>
-    <t>Nguyễn Anh Duy</t>
+    <t>19/10/2026</t>
+  </si>
+  <si>
+    <t>23/10/2026</t>
   </si>
   <si>
     <t>02223535</t>
@@ -229,6 +283,12 @@
     <t>Nguyễn Quốc</t>
   </si>
   <si>
+    <t>22/10/2026</t>
+  </si>
+  <si>
+    <t>bản thân ốm</t>
+  </si>
+  <si>
     <t>02021131</t>
   </si>
   <si>
@@ -241,6 +301,24 @@
     <t>Nguyễn Xuân Mạnh</t>
   </si>
   <si>
+    <t>02660444</t>
+  </si>
+  <si>
+    <t>Võ Minh Đức</t>
+  </si>
+  <si>
+    <t>26/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">欠勤 /  Nghỉ không lương – HĐTV</t>
+  </si>
+  <si>
+    <t>Bận việc gia đình</t>
+  </si>
+  <si>
+    <t>Chờ cấp trên gián tiếp</t>
+  </si>
+  <si>
     <t>02645241</t>
   </si>
   <si>
@@ -250,61 +328,31 @@
     <t>14/10/2026</t>
   </si>
   <si>
-    <t>Chờ cấp trên gián tiếp</t>
-  </si>
-  <si>
     <t>02020390</t>
   </si>
   <si>
     <t>Võ Thiên Tuế</t>
   </si>
   <si>
-    <t>02243991</t>
-  </si>
-  <si>
-    <t>Bùi Quang Chưởng</t>
-  </si>
-  <si>
-    <t>Chưa duyệt</t>
-  </si>
-  <si>
-    <t>02221908</t>
-  </si>
-  <si>
-    <t>Nguyễn Minh Hoàng</t>
-  </si>
-  <si>
-    <t>02/10/2026</t>
-  </si>
-  <si>
-    <t>01921551</t>
-  </si>
-  <si>
-    <t>Trương Quang Nghĩa</t>
-  </si>
-  <si>
-    <t>nghỉ phép sn</t>
-  </si>
-  <si>
-    <t>02325374</t>
-  </si>
-  <si>
-    <t>Trương Văn Tình</t>
-  </si>
-  <si>
-    <t>02020752</t>
-  </si>
-  <si>
-    <t>Nguyễn Chí Cường</t>
-  </si>
-  <si>
-    <t>Pulverize</t>
-  </si>
-  <si>
-    <t>02020488</t>
-  </si>
-  <si>
-    <t>Lê Thanh Trúc</t>
+    <t>21/10/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無給休暇 /  Nghỉ con ốm hưởng BHXH</t>
+  </si>
+  <si>
+    <t>con ốm</t>
+  </si>
+  <si>
+    <t>Đăng ký sai</t>
+  </si>
+  <si>
+    <t>Từ chối</t>
+  </si>
+  <si>
+    <t>02325365</t>
+  </si>
+  <si>
+    <t>Trần Minh Nhật</t>
   </si>
   <si>
     <t>02224358</t>
@@ -325,30 +373,42 @@
     <t>Nguyễn Hoàng Duy</t>
   </si>
   <si>
+    <t>01920668</t>
+  </si>
+  <si>
+    <t>Hà Viết Thế Thiện</t>
+  </si>
+  <si>
+    <t>02121404</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Minh Tâm</t>
+  </si>
+  <si>
+    <t>02223526</t>
+  </si>
+  <si>
+    <t>Nguyễn Thiên Phú</t>
+  </si>
+  <si>
+    <t>16/10/2026</t>
+  </si>
+  <si>
     <t>02228947</t>
   </si>
   <si>
     <t>Phạm Lê Minh Tân</t>
   </si>
   <si>
+    <t>20/10/2026</t>
+  </si>
+  <si>
     <t>02644057</t>
   </si>
   <si>
     <t>Phạm Văn Công</t>
   </si>
   <si>
-    <t>01920668</t>
-  </si>
-  <si>
-    <t>Hà Viết Thế Thiện</t>
-  </si>
-  <si>
-    <t>02121404</t>
-  </si>
-  <si>
-    <t>Lê Hoàng Minh Tâm</t>
-  </si>
-  <si>
     <t>02226596</t>
   </si>
   <si>
@@ -359,6 +419,12 @@
   </si>
   <si>
     <t>Võ Minh Bắc</t>
+  </si>
+  <si>
+    <t>02222350</t>
+  </si>
+  <si>
+    <t>Hoàng Văn Nguyên</t>
   </si>
 </sst>
 </file>
@@ -896,13 +962,13 @@
         <v>1</v>
       </c>
       <c r="H4" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I4" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>23</v>
@@ -919,10 +985,10 @@
     </row>
     <row r="5" s="2" customFormat="1">
       <c r="A5" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>17</v>
@@ -931,19 +997,19 @@
         <v>18</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="G5" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J5" s="7" t="s">
         <v>22</v>
@@ -963,10 +1029,10 @@
     </row>
     <row r="6" s="2" customFormat="1">
       <c r="A6" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>17</v>
@@ -1007,31 +1073,31 @@
     </row>
     <row r="7" s="2" customFormat="1">
       <c r="A7" s="7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>33</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>21</v>
       </c>
       <c r="J7" s="7" t="s">
         <v>22</v>
@@ -1051,10 +1117,10 @@
     </row>
     <row r="8" s="2" customFormat="1">
       <c r="A8" s="7" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>17</v>
@@ -1063,22 +1129,22 @@
         <v>18</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="G8" s="8">
         <v>1</v>
       </c>
       <c r="H8" s="7" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I8" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K8" s="7" t="s">
         <v>23</v>
@@ -1095,10 +1161,10 @@
     </row>
     <row r="9" s="2" customFormat="1">
       <c r="A9" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>17</v>
@@ -1107,19 +1173,19 @@
         <v>18</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G9" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J9" s="7" t="s">
         <v>22</v>
@@ -1139,10 +1205,10 @@
     </row>
     <row r="10" s="2" customFormat="1">
       <c r="A10" s="7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>17</v>
@@ -1157,13 +1223,13 @@
         <v>43</v>
       </c>
       <c r="G10" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H10" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="J10" s="7" t="s">
         <v>22</v>
@@ -1183,10 +1249,10 @@
     </row>
     <row r="11" s="2" customFormat="1">
       <c r="A11" s="7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>17</v>
@@ -1195,10 +1261,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G11" s="8">
         <v>1</v>
@@ -1239,19 +1305,19 @@
         <v>18</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G12" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H12" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J12" s="7" t="s">
         <v>22</v>
@@ -1271,22 +1337,22 @@
     </row>
     <row r="13" s="2" customFormat="1">
       <c r="A13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="C13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="F13" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G13" s="8">
         <v>1</v>
@@ -1315,10 +1381,10 @@
     </row>
     <row r="14" s="2" customFormat="1">
       <c r="A14" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>17</v>
@@ -1327,22 +1393,22 @@
         <v>18</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G14" s="8">
         <v>1</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>54</v>
+        <v>20</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J14" s="7" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="K14" s="7" t="s">
         <v>23</v>
@@ -1359,34 +1425,34 @@
     </row>
     <row r="15" s="2" customFormat="1">
       <c r="A15" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="G15" s="8">
+        <v>1</v>
+      </c>
+      <c r="H15" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="I15" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="7" t="s">
         <v>57</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="8">
-        <v>1</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>22</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>23</v>
@@ -1403,10 +1469,10 @@
     </row>
     <row r="16" s="2" customFormat="1">
       <c r="A16" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>17</v>
@@ -1415,22 +1481,22 @@
         <v>18</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="G16" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="K16" s="7" t="s">
         <v>23</v>
@@ -1447,10 +1513,10 @@
     </row>
     <row r="17" s="2" customFormat="1">
       <c r="A17" s="7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>17</v>
@@ -1459,22 +1525,22 @@
         <v>18</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="G17" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>61</v>
+        <v>22</v>
       </c>
       <c r="K17" s="7" t="s">
         <v>23</v>
@@ -1491,10 +1557,10 @@
     </row>
     <row r="18" s="2" customFormat="1">
       <c r="A18" s="7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>17</v>
@@ -1503,19 +1569,19 @@
         <v>18</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="F18" s="8" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="G18" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="J18" s="7" t="s">
         <v>22</v>
@@ -1535,10 +1601,10 @@
     </row>
     <row r="19" s="2" customFormat="1">
       <c r="A19" s="7" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>17</v>
@@ -1547,19 +1613,19 @@
         <v>18</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="G19" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J19" s="7" t="s">
         <v>22</v>
@@ -1579,10 +1645,10 @@
     </row>
     <row r="20" s="2" customFormat="1">
       <c r="A20" s="7" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>17</v>
@@ -1591,10 +1657,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="G20" s="8">
         <v>1</v>
@@ -1623,10 +1689,10 @@
     </row>
     <row r="21" s="2" customFormat="1">
       <c r="A21" s="7" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>17</v>
@@ -1635,22 +1701,22 @@
         <v>18</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="G21" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>20</v>
+        <v>72</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="K21" s="7" t="s">
         <v>23</v>
@@ -1667,10 +1733,10 @@
     </row>
     <row r="22" s="2" customFormat="1">
       <c r="A22" s="7" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>17</v>
@@ -1679,10 +1745,10 @@
         <v>18</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="F22" s="8" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="G22" s="8">
         <v>1</v>
@@ -1711,10 +1777,10 @@
     </row>
     <row r="23" s="2" customFormat="1">
       <c r="A23" s="7" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>31</v>
+        <v>75</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>17</v>
@@ -1723,22 +1789,22 @@
         <v>18</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="G23" s="8">
         <v>1</v>
       </c>
       <c r="H23" s="7" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>23</v>
@@ -1755,10 +1821,10 @@
     </row>
     <row r="24" s="2" customFormat="1">
       <c r="A24" s="7" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>17</v>
@@ -1767,22 +1833,22 @@
         <v>18</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="F24" s="8" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="G24" s="8">
         <v>1</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="K24" s="7" t="s">
         <v>23</v>
@@ -1799,10 +1865,10 @@
     </row>
     <row r="25" s="2" customFormat="1">
       <c r="A25" s="7" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>17</v>
@@ -1811,19 +1877,19 @@
         <v>18</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="F25" s="8" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="G25" s="8">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="J25" s="7" t="s">
         <v>22</v>
@@ -1843,10 +1909,10 @@
     </row>
     <row r="26" s="2" customFormat="1">
       <c r="A26" s="7" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>17</v>
@@ -1855,22 +1921,22 @@
         <v>18</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>43</v>
+        <v>81</v>
       </c>
       <c r="G26" s="8">
         <v>1</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>21</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="K26" s="7" t="s">
         <v>23</v>
@@ -1887,10 +1953,10 @@
     </row>
     <row r="27" s="2" customFormat="1">
       <c r="A27" s="7" t="s">
-        <v>70</v>
+        <v>44</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>71</v>
+        <v>45</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>17</v>
@@ -1899,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="G27" s="8">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>20</v>
@@ -1931,10 +1997,10 @@
     </row>
     <row r="28" s="2" customFormat="1">
       <c r="A28" s="7" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>17</v>
@@ -1943,19 +2009,19 @@
         <v>18</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="G28" s="8">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>20</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="J28" s="7" t="s">
         <v>22</v>
@@ -1975,10 +2041,10 @@
     </row>
     <row r="29" s="2" customFormat="1">
       <c r="A29" s="7" t="s">
-        <v>72</v>
+        <v>41</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>73</v>
+        <v>42</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>17</v>
@@ -1987,10 +2053,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="F29" s="8" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="G29" s="8">
         <v>0.5</v>
@@ -1999,7 +2065,7 @@
         <v>20</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J29" s="7" t="s">
         <v>22</v>
@@ -2019,10 +2085,10 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>17</v>
@@ -2031,22 +2097,22 @@
         <v>18</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G30" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="K30" s="3" t="s">
         <v>23</v>
@@ -2063,10 +2129,10 @@
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>17</v>
@@ -2075,19 +2141,19 @@
         <v>18</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>50</v>
+        <v>84</v>
       </c>
       <c r="G31" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J31" s="3" t="s">
         <v>22</v>
@@ -2107,22 +2173,22 @@
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="G32" s="4">
         <v>1</v>
@@ -2146,15 +2212,15 @@
         <v>22</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>17</v>
@@ -2163,19 +2229,19 @@
         <v>18</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="G33" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>22</v>
@@ -2190,15 +2256,15 @@
         <v>22</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>17</v>
@@ -2207,13 +2273,13 @@
         <v>18</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="G34" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>20</v>
@@ -2234,57 +2300,59 @@
         <v>22</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G35" s="4">
+        <v>1</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="I35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J35" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G35" s="4">
-        <v>0.5</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="K35" s="3" t="s">
         <v>23</v>
       </c>
       <c r="L35" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="M35" s="3"/>
+      <c r="M35" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="N35" s="4" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>17</v>
@@ -2293,22 +2361,22 @@
         <v>18</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G36" s="4">
         <v>1</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>22</v>
+        <v>89</v>
       </c>
       <c r="K36" s="3" t="s">
         <v>23</v>
@@ -2325,10 +2393,10 @@
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>86</v>
+        <v>46</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>87</v>
+        <v>47</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>17</v>
@@ -2337,22 +2405,22 @@
         <v>18</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G37" s="4">
         <v>1</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>88</v>
+        <v>22</v>
       </c>
       <c r="K37" s="3" t="s">
         <v>23</v>
@@ -2369,10 +2437,10 @@
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>17</v>
@@ -2381,19 +2449,19 @@
         <v>18</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="G38" s="4">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>22</v>
@@ -2413,10 +2481,10 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>89</v>
+        <v>46</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>90</v>
+        <v>47</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>17</v>
@@ -2425,19 +2493,19 @@
         <v>18</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="G39" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="J39" s="3" t="s">
         <v>22</v>
@@ -2457,22 +2525,22 @@
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="G40" s="4">
         <v>0.5</v>
@@ -2481,7 +2549,7 @@
         <v>20</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="J40" s="3" t="s">
         <v>22</v>
@@ -2513,22 +2581,22 @@
         <v>18</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="G41" s="4">
         <v>1</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>20</v>
+        <v>97</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>21</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>22</v>
+        <v>98</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>23</v>
@@ -2540,45 +2608,45 @@
         <v>22</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="G42" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M42" s="3" t="s">
         <v>22</v>
@@ -2589,22 +2657,22 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>100</v>
+        <v>64</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="G43" s="4">
         <v>1</v>
@@ -2619,10 +2687,10 @@
         <v>22</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M43" s="3" t="s">
         <v>22</v>
@@ -2633,22 +2701,22 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B44" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>47</v>
-      </c>
       <c r="F44" s="4" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="G44" s="4">
         <v>1</v>
@@ -2663,10 +2731,10 @@
         <v>22</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>22</v>
@@ -2677,40 +2745,40 @@
     </row>
     <row r="45">
       <c r="A45" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="C45" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="G45" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="J45" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M45" s="3" t="s">
         <v>22</v>
@@ -2721,22 +2789,22 @@
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>107</v>
+        <v>31</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>53</v>
+        <v>102</v>
       </c>
       <c r="G46" s="4">
         <v>1</v>
@@ -2751,10 +2819,10 @@
         <v>22</v>
       </c>
       <c r="K46" s="3" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M46" s="3" t="s">
         <v>22</v>
@@ -2765,40 +2833,40 @@
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="G47" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>22</v>
@@ -2809,40 +2877,40 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>109</v>
+        <v>91</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>93</v>
+        <v>18</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>47</v>
+        <v>81</v>
       </c>
       <c r="G48" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>20</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>92</v>
+        <v>23</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>22</v>
@@ -2853,66 +2921,66 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>111</v>
+        <v>49</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="G49" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>20</v>
+        <v>106</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J49" s="3" t="s">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>22</v>
+        <v>108</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>25</v>
+        <v>109</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>17</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G50" s="4">
         <v>0.5</v>
@@ -2921,16 +2989,16 @@
         <v>20</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>99</v>
+        <v>23</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M50" s="3" t="s">
         <v>22</v>
@@ -2950,37 +3018,609 @@
         <v>17</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="E51" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G51" s="4">
+        <v>1</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G52" s="4">
+        <v>1</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G53" s="4">
+        <v>1</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="F54" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="G51" s="4">
+      <c r="G54" s="4">
+        <v>1</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G55" s="4">
+        <v>1</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N55" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G56" s="4">
         <v>0.5</v>
       </c>
-      <c r="H51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N51" s="4" t="s">
-        <v>82</v>
+      <c r="H56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G57" s="4">
+        <v>1</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G58" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N58" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G59" s="4">
+        <v>1</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N59" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G60" s="4">
+        <v>1</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N60" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G61" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N61" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G62" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N62" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B63" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G63" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M63" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N63" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G64" s="4">
+        <v>1</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N64" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
